--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2143"/>
+  <dimension ref="A1:K2163"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -74353,7 +74353,7 @@
         <v>1571.68</v>
       </c>
       <c r="F1923">
-        <f t="shared" ref="F1923:F2143" si="89">E1923/1000</f>
+        <f t="shared" ref="F1923:F2163" si="89">E1923/1000</f>
         <v>1.57168</v>
       </c>
       <c r="G1923">
@@ -81313,7 +81313,7 @@
         <v>1.119025302525011</v>
       </c>
       <c r="K2101">
-        <f t="shared" ref="K2101:K2143" si="90">SUM(F1852:F2101)/250</f>
+        <f t="shared" ref="K2101:K2163" si="90">SUM(F1852:F2101)/250</f>
         <v>1.6052981200000014</v>
       </c>
     </row>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2143" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2163" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -82953,6 +82953,786 @@
       <c r="K2143">
         <f t="shared" si="90"/>
         <v>1.6746592000000005</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2144" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B2144">
+        <v>1886.2</v>
+      </c>
+      <c r="C2144">
+        <v>1925.98</v>
+      </c>
+      <c r="D2144">
+        <v>1884.1</v>
+      </c>
+      <c r="E2144">
+        <v>1925.98</v>
+      </c>
+      <c r="F2144">
+        <f t="shared" si="89"/>
+        <v>1.92598</v>
+      </c>
+      <c r="G2144">
+        <v>344027235</v>
+      </c>
+      <c r="H2144" s="3">
+        <v>608005000000</v>
+      </c>
+      <c r="I2144">
+        <f t="shared" si="91"/>
+        <v>2142</v>
+      </c>
+      <c r="J2144">
+        <f>SUM($F$3:F2144)/I2144</f>
+        <v>1.1338452567693733</v>
+      </c>
+      <c r="K2144">
+        <f t="shared" si="90"/>
+        <v>1.6765696400000005</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2145" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B2145">
+        <v>1929.05</v>
+      </c>
+      <c r="C2145">
+        <v>1951.25</v>
+      </c>
+      <c r="D2145">
+        <v>1927.27</v>
+      </c>
+      <c r="E2145">
+        <v>1951.25</v>
+      </c>
+      <c r="F2145">
+        <f t="shared" si="89"/>
+        <v>1.9512499999999999</v>
+      </c>
+      <c r="G2145">
+        <v>372278153</v>
+      </c>
+      <c r="H2145" s="3">
+        <v>666192000000</v>
+      </c>
+      <c r="I2145">
+        <f t="shared" si="91"/>
+        <v>2143</v>
+      </c>
+      <c r="J2145">
+        <f>SUM($F$3:F2145)/I2145</f>
+        <v>1.1342266868875397</v>
+      </c>
+      <c r="K2145">
+        <f t="shared" si="90"/>
+        <v>1.6785481200000005</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2146" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B2146">
+        <v>1951.52</v>
+      </c>
+      <c r="C2146">
+        <v>1957.83</v>
+      </c>
+      <c r="D2146">
+        <v>1939.22</v>
+      </c>
+      <c r="E2146">
+        <v>1947.04</v>
+      </c>
+      <c r="F2146">
+        <f t="shared" si="89"/>
+        <v>1.9470399999999999</v>
+      </c>
+      <c r="G2146">
+        <v>346243433</v>
+      </c>
+      <c r="H2146" s="3">
+        <v>644731000000</v>
+      </c>
+      <c r="I2146">
+        <f t="shared" si="91"/>
+        <v>2144</v>
+      </c>
+      <c r="J2146">
+        <f>SUM($F$3:F2146)/I2146</f>
+        <v>1.1346057975746258</v>
+      </c>
+      <c r="K2146">
+        <f t="shared" si="90"/>
+        <v>1.6806621200000007</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2147" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B2147">
+        <v>1945.77</v>
+      </c>
+      <c r="C2147">
+        <v>1984.12</v>
+      </c>
+      <c r="D2147">
+        <v>1945.36</v>
+      </c>
+      <c r="E2147">
+        <v>1979.4</v>
+      </c>
+      <c r="F2147">
+        <f t="shared" si="89"/>
+        <v>1.9794</v>
+      </c>
+      <c r="G2147">
+        <v>377307368</v>
+      </c>
+      <c r="H2147" s="3">
+        <v>701066000000</v>
+      </c>
+      <c r="I2147">
+        <f t="shared" si="91"/>
+        <v>2145</v>
+      </c>
+      <c r="J2147">
+        <f>SUM($F$3:F2147)/I2147</f>
+        <v>1.13499964102564</v>
+      </c>
+      <c r="K2147">
+        <f t="shared" si="90"/>
+        <v>1.6828030800000007</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2148" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B2148">
+        <v>1981.37</v>
+      </c>
+      <c r="C2148">
+        <v>2030.87</v>
+      </c>
+      <c r="D2148">
+        <v>1981.37</v>
+      </c>
+      <c r="E2148">
+        <v>2030.87</v>
+      </c>
+      <c r="F2148">
+        <f t="shared" si="89"/>
+        <v>2.0308699999999997</v>
+      </c>
+      <c r="G2148">
+        <v>453699002</v>
+      </c>
+      <c r="H2148" s="3">
+        <v>834566000000</v>
+      </c>
+      <c r="I2148">
+        <f t="shared" si="91"/>
+        <v>2146</v>
+      </c>
+      <c r="J2148">
+        <f>SUM($F$3:F2148)/I2148</f>
+        <v>1.1354171015843419</v>
+      </c>
+      <c r="K2148">
+        <f t="shared" si="90"/>
+        <v>1.6851434000000005</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2149" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B2149">
+        <v>2058.06</v>
+      </c>
+      <c r="C2149">
+        <v>2130.3200000000002</v>
+      </c>
+      <c r="D2149">
+        <v>2058.06</v>
+      </c>
+      <c r="E2149">
+        <v>2129.84</v>
+      </c>
+      <c r="F2149">
+        <f t="shared" si="89"/>
+        <v>2.1298400000000002</v>
+      </c>
+      <c r="G2149">
+        <v>539059173</v>
+      </c>
+      <c r="H2149" s="3">
+        <v>1061600000000</v>
+      </c>
+      <c r="I2149">
+        <f t="shared" si="91"/>
+        <v>2147</v>
+      </c>
+      <c r="J2149">
+        <f>SUM($F$3:F2149)/I2149</f>
+        <v>1.1358802701443866</v>
+      </c>
+      <c r="K2149">
+        <f t="shared" si="90"/>
+        <v>1.6879256800000006</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2150" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B2150">
+        <v>2154.36</v>
+      </c>
+      <c r="C2150">
+        <v>2155.34</v>
+      </c>
+      <c r="D2150">
+        <v>2097.65</v>
+      </c>
+      <c r="E2150">
+        <v>2102.7199999999998</v>
+      </c>
+      <c r="F2150">
+        <f t="shared" si="89"/>
+        <v>2.1027199999999997</v>
+      </c>
+      <c r="G2150">
+        <v>606580917</v>
+      </c>
+      <c r="H2150" s="3">
+        <v>1147510000000</v>
+      </c>
+      <c r="I2150">
+        <f t="shared" si="91"/>
+        <v>2148</v>
+      </c>
+      <c r="J2150">
+        <f>SUM($F$3:F2150)/I2150</f>
+        <v>1.1363303817504646</v>
+      </c>
+      <c r="K2150">
+        <f t="shared" si="90"/>
+        <v>1.6907980000000007</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2151" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B2151">
+        <v>2101.61</v>
+      </c>
+      <c r="C2151">
+        <v>2184.2800000000002</v>
+      </c>
+      <c r="D2151">
+        <v>2101.61</v>
+      </c>
+      <c r="E2151">
+        <v>2146.14</v>
+      </c>
+      <c r="F2151">
+        <f t="shared" si="89"/>
+        <v>2.1461399999999999</v>
+      </c>
+      <c r="G2151">
+        <v>670692200</v>
+      </c>
+      <c r="H2151" s="3">
+        <v>1271990000000</v>
+      </c>
+      <c r="I2151">
+        <f t="shared" si="91"/>
+        <v>2149</v>
+      </c>
+      <c r="J2151">
+        <f>SUM($F$3:F2151)/I2151</f>
+        <v>1.1368002791996266</v>
+      </c>
+      <c r="K2151">
+        <f t="shared" si="90"/>
+        <v>1.6939660400000005</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2152" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B2152">
+        <v>2125.79</v>
+      </c>
+      <c r="C2152">
+        <v>2131.4899999999998</v>
+      </c>
+      <c r="D2152">
+        <v>2087.77</v>
+      </c>
+      <c r="E2152">
+        <v>2103.4299999999998</v>
+      </c>
+      <c r="F2152">
+        <f t="shared" si="89"/>
+        <v>2.1034299999999999</v>
+      </c>
+      <c r="G2152">
+        <v>480859218</v>
+      </c>
+      <c r="H2152" s="3">
+        <v>860970000000</v>
+      </c>
+      <c r="I2152">
+        <f t="shared" si="91"/>
+        <v>2150</v>
+      </c>
+      <c r="J2152">
+        <f>SUM($F$3:F2152)/I2152</f>
+        <v>1.1372498744186037</v>
+      </c>
+      <c r="K2152">
+        <f t="shared" si="90"/>
+        <v>1.6972208000000002</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2153" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B2153">
+        <v>2102.84</v>
+      </c>
+      <c r="C2153">
+        <v>2108</v>
+      </c>
+      <c r="D2153">
+        <v>2061.56</v>
+      </c>
+      <c r="E2153">
+        <v>2075.1799999999998</v>
+      </c>
+      <c r="F2153">
+        <f t="shared" si="89"/>
+        <v>2.07518</v>
+      </c>
+      <c r="G2153">
+        <v>423195774</v>
+      </c>
+      <c r="H2153" s="3">
+        <v>773729000000</v>
+      </c>
+      <c r="I2153">
+        <f t="shared" si="91"/>
+        <v>2151</v>
+      </c>
+      <c r="J2153">
+        <f>SUM($F$3:F2153)/I2153</f>
+        <v>1.1376859181775907</v>
+      </c>
+      <c r="K2153">
+        <f t="shared" si="90"/>
+        <v>1.7004414400000005</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2154" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B2154">
+        <v>2063.6</v>
+      </c>
+      <c r="C2154">
+        <v>2082.44</v>
+      </c>
+      <c r="D2154">
+        <v>2056.34</v>
+      </c>
+      <c r="E2154">
+        <v>2073.54</v>
+      </c>
+      <c r="F2154">
+        <f t="shared" si="89"/>
+        <v>2.0735399999999999</v>
+      </c>
+      <c r="G2154">
+        <v>351535778</v>
+      </c>
+      <c r="H2154" s="3">
+        <v>643832000000</v>
+      </c>
+      <c r="I2154">
+        <f t="shared" si="91"/>
+        <v>2152</v>
+      </c>
+      <c r="J2154">
+        <f>SUM($F$3:F2154)/I2154</f>
+        <v>1.1381207946096643</v>
+      </c>
+      <c r="K2154">
+        <f t="shared" si="90"/>
+        <v>1.7034916800000006</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2155" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B2155">
+        <v>2078.46</v>
+      </c>
+      <c r="C2155">
+        <v>2083.3000000000002</v>
+      </c>
+      <c r="D2155">
+        <v>2036.14</v>
+      </c>
+      <c r="E2155">
+        <v>2051.08</v>
+      </c>
+      <c r="F2155">
+        <f t="shared" si="89"/>
+        <v>2.0510799999999998</v>
+      </c>
+      <c r="G2155">
+        <v>372833622</v>
+      </c>
+      <c r="H2155" s="3">
+        <v>656362000000</v>
+      </c>
+      <c r="I2155">
+        <f t="shared" si="91"/>
+        <v>2153</v>
+      </c>
+      <c r="J2155">
+        <f>SUM($F$3:F2155)/I2155</f>
+        <v>1.1385448351137937</v>
+      </c>
+      <c r="K2155">
+        <f t="shared" si="90"/>
+        <v>1.7064384000000001</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2156" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B2156">
+        <v>2038.19</v>
+      </c>
+      <c r="C2156">
+        <v>2071.65</v>
+      </c>
+      <c r="D2156">
+        <v>2034.24</v>
+      </c>
+      <c r="E2156">
+        <v>2061.5100000000002</v>
+      </c>
+      <c r="F2156">
+        <f t="shared" si="89"/>
+        <v>2.0615100000000002</v>
+      </c>
+      <c r="G2156">
+        <v>315447582</v>
+      </c>
+      <c r="H2156" s="3">
+        <v>605114000000</v>
+      </c>
+      <c r="I2156">
+        <f t="shared" si="91"/>
+        <v>2154</v>
+      </c>
+      <c r="J2156">
+        <f>SUM($F$3:F2156)/I2156</f>
+        <v>1.1389733240482811</v>
+      </c>
+      <c r="K2156">
+        <f t="shared" si="90"/>
+        <v>1.7093727200000002</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2157" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B2157">
+        <v>2067.67</v>
+      </c>
+      <c r="C2157">
+        <v>2082.1</v>
+      </c>
+      <c r="D2157">
+        <v>2062.13</v>
+      </c>
+      <c r="E2157">
+        <v>2080.15</v>
+      </c>
+      <c r="F2157">
+        <f t="shared" si="89"/>
+        <v>2.0801500000000002</v>
+      </c>
+      <c r="G2157">
+        <v>327907245</v>
+      </c>
+      <c r="H2157" s="3">
+        <v>624429000000</v>
+      </c>
+      <c r="I2157">
+        <f t="shared" si="91"/>
+        <v>2155</v>
+      </c>
+      <c r="J2157">
+        <f>SUM($F$3:F2157)/I2157</f>
+        <v>1.1394100649651961</v>
+      </c>
+      <c r="K2157">
+        <f t="shared" si="90"/>
+        <v>1.7125506000000004</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2158" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B2158">
+        <v>2085.79</v>
+      </c>
+      <c r="C2158">
+        <v>2117.09</v>
+      </c>
+      <c r="D2158">
+        <v>2081.0500000000002</v>
+      </c>
+      <c r="E2158">
+        <v>2117.09</v>
+      </c>
+      <c r="F2158">
+        <f t="shared" si="89"/>
+        <v>2.1170900000000001</v>
+      </c>
+      <c r="G2158">
+        <v>410438538</v>
+      </c>
+      <c r="H2158" s="3">
+        <v>736127000000</v>
+      </c>
+      <c r="I2158">
+        <f t="shared" si="91"/>
+        <v>2156</v>
+      </c>
+      <c r="J2158">
+        <f>SUM($F$3:F2158)/I2158</f>
+        <v>1.1398635343228189</v>
+      </c>
+      <c r="K2158">
+        <f t="shared" si="90"/>
+        <v>1.71586704</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2159" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B2159">
+        <v>2121.63</v>
+      </c>
+      <c r="C2159">
+        <v>2123.5300000000002</v>
+      </c>
+      <c r="D2159">
+        <v>2060.27</v>
+      </c>
+      <c r="E2159">
+        <v>2079.35</v>
+      </c>
+      <c r="F2159">
+        <f t="shared" si="89"/>
+        <v>2.0793499999999998</v>
+      </c>
+      <c r="G2159">
+        <v>407442857</v>
+      </c>
+      <c r="H2159" s="3">
+        <v>725157000000</v>
+      </c>
+      <c r="I2159">
+        <f t="shared" si="91"/>
+        <v>2157</v>
+      </c>
+      <c r="J2159">
+        <f>SUM($F$3:F2159)/I2159</f>
+        <v>1.140299086694482</v>
+      </c>
+      <c r="K2159">
+        <f t="shared" si="90"/>
+        <v>1.7187187599999998</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2160" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B2160">
+        <v>2073.37</v>
+      </c>
+      <c r="C2160">
+        <v>2083.7199999999998</v>
+      </c>
+      <c r="D2160">
+        <v>2032.05</v>
+      </c>
+      <c r="E2160">
+        <v>2081.46</v>
+      </c>
+      <c r="F2160">
+        <f t="shared" si="89"/>
+        <v>2.0814599999999999</v>
+      </c>
+      <c r="G2160">
+        <v>355605667</v>
+      </c>
+      <c r="H2160" s="3">
+        <v>640260000000</v>
+      </c>
+      <c r="I2160">
+        <f t="shared" si="91"/>
+        <v>2158</v>
+      </c>
+      <c r="J2160">
+        <f>SUM($F$3:F2160)/I2160</f>
+        <v>1.1407352131603326</v>
+      </c>
+      <c r="K2160">
+        <f t="shared" si="90"/>
+        <v>1.7215820399999997</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2161" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B2161">
+        <v>2079.91</v>
+      </c>
+      <c r="C2161">
+        <v>2091.7399999999998</v>
+      </c>
+      <c r="D2161">
+        <v>2055.5300000000002</v>
+      </c>
+      <c r="E2161">
+        <v>2057.41</v>
+      </c>
+      <c r="F2161">
+        <f t="shared" si="89"/>
+        <v>2.05741</v>
+      </c>
+      <c r="G2161">
+        <v>360474218</v>
+      </c>
+      <c r="H2161" s="3">
+        <v>645064000000</v>
+      </c>
+      <c r="I2161">
+        <f t="shared" si="91"/>
+        <v>2159</v>
+      </c>
+      <c r="J2161">
+        <f>SUM($F$3:F2161)/I2161</f>
+        <v>1.1411597962019442</v>
+      </c>
+      <c r="K2161">
+        <f t="shared" si="90"/>
+        <v>1.7243222799999993</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2162" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B2162">
+        <v>2045.99</v>
+      </c>
+      <c r="C2162">
+        <v>2095.9699999999998</v>
+      </c>
+      <c r="D2162">
+        <v>2027.96</v>
+      </c>
+      <c r="E2162">
+        <v>2050.92</v>
+      </c>
+      <c r="F2162">
+        <f t="shared" si="89"/>
+        <v>2.0509200000000001</v>
+      </c>
+      <c r="G2162">
+        <v>422167163</v>
+      </c>
+      <c r="H2162" s="3">
+        <v>743307000000</v>
+      </c>
+      <c r="I2162">
+        <f t="shared" si="91"/>
+        <v>2160</v>
+      </c>
+      <c r="J2162">
+        <f>SUM($F$3:F2162)/I2162</f>
+        <v>1.1415809814814804</v>
+      </c>
+      <c r="K2162">
+        <f t="shared" si="90"/>
+        <v>1.7270541599999998</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2163" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B2163">
+        <v>2039.1</v>
+      </c>
+      <c r="C2163">
+        <v>2047.35</v>
+      </c>
+      <c r="D2163">
+        <v>2007.96</v>
+      </c>
+      <c r="E2163">
+        <v>2035.88</v>
+      </c>
+      <c r="F2163">
+        <f t="shared" si="89"/>
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="G2163">
+        <v>355089225</v>
+      </c>
+      <c r="H2163" s="3">
+        <v>623711000000</v>
+      </c>
+      <c r="I2163">
+        <f t="shared" si="91"/>
+        <v>2161</v>
+      </c>
+      <c r="J2163">
+        <f>SUM($F$3:F2163)/I2163</f>
+        <v>1.1419948172142516</v>
+      </c>
+      <c r="K2163">
+        <f t="shared" si="90"/>
+        <v>1.7296812799999999</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2163"/>
+  <dimension ref="A1:K2178"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -74353,7 +74353,7 @@
         <v>1571.68</v>
       </c>
       <c r="F1923">
-        <f t="shared" ref="F1923:F2163" si="89">E1923/1000</f>
+        <f t="shared" ref="F1923:F2177" si="89">E1923/1000</f>
         <v>1.57168</v>
       </c>
       <c r="G1923">
@@ -81313,7 +81313,7 @@
         <v>1.119025302525011</v>
       </c>
       <c r="K2101">
-        <f t="shared" ref="K2101:K2163" si="90">SUM(F1852:F2101)/250</f>
+        <f t="shared" ref="K2101:K2178" si="90">SUM(F1852:F2101)/250</f>
         <v>1.6052981200000014</v>
       </c>
     </row>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2163" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2178" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -83733,6 +83733,591 @@
       <c r="K2163">
         <f t="shared" si="90"/>
         <v>1.7296812799999999</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2164" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B2164">
+        <v>2060.0500000000002</v>
+      </c>
+      <c r="C2164">
+        <v>2087.19</v>
+      </c>
+      <c r="D2164">
+        <v>2057.65</v>
+      </c>
+      <c r="E2164">
+        <v>2087.19</v>
+      </c>
+      <c r="F2164">
+        <f t="shared" si="89"/>
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="G2164">
+        <v>314303052</v>
+      </c>
+      <c r="H2164" s="3">
+        <v>571074000000</v>
+      </c>
+      <c r="I2164">
+        <f t="shared" si="91"/>
+        <v>2162</v>
+      </c>
+      <c r="J2164">
+        <f>SUM($F$3:F2164)/I2164</f>
+        <v>1.1424320027752071</v>
+      </c>
+      <c r="K2164">
+        <f t="shared" si="90"/>
+        <v>1.7324908400000001</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2165" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B2165">
+        <v>2023.78</v>
+      </c>
+      <c r="C2165">
+        <v>2042.56</v>
+      </c>
+      <c r="D2165">
+        <v>1992.38</v>
+      </c>
+      <c r="E2165">
+        <v>1992.38</v>
+      </c>
+      <c r="F2165">
+        <f t="shared" si="89"/>
+        <v>1.99238</v>
+      </c>
+      <c r="G2165">
+        <v>326813703</v>
+      </c>
+      <c r="H2165" s="3">
+        <v>571826000000</v>
+      </c>
+      <c r="I2165">
+        <f t="shared" si="91"/>
+        <v>2163</v>
+      </c>
+      <c r="J2165">
+        <f>SUM($F$3:F2165)/I2165</f>
+        <v>1.1428249514563096</v>
+      </c>
+      <c r="K2165">
+        <f t="shared" si="90"/>
+        <v>1.7349923200000001</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2166" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B2166">
+        <v>2011.79</v>
+      </c>
+      <c r="C2166">
+        <v>2041.13</v>
+      </c>
+      <c r="D2166">
+        <v>2003.77</v>
+      </c>
+      <c r="E2166">
+        <v>2041.13</v>
+      </c>
+      <c r="F2166">
+        <f t="shared" si="89"/>
+        <v>2.0411299999999999</v>
+      </c>
+      <c r="G2166">
+        <v>326584324</v>
+      </c>
+      <c r="H2166" s="3">
+        <v>596548000000</v>
+      </c>
+      <c r="I2166">
+        <f t="shared" si="91"/>
+        <v>2164</v>
+      </c>
+      <c r="J2166">
+        <f>SUM($F$3:F2166)/I2166</f>
+        <v>1.1432400646950083</v>
+      </c>
+      <c r="K2166">
+        <f t="shared" si="90"/>
+        <v>1.7376932000000003</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2167" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B2167">
+        <v>2032.12</v>
+      </c>
+      <c r="C2167">
+        <v>2036.38</v>
+      </c>
+      <c r="D2167">
+        <v>2008.37</v>
+      </c>
+      <c r="E2167">
+        <v>2029.79</v>
+      </c>
+      <c r="F2167">
+        <f t="shared" si="89"/>
+        <v>2.0297899999999998</v>
+      </c>
+      <c r="G2167">
+        <v>321148922</v>
+      </c>
+      <c r="H2167" s="3">
+        <v>559149000000</v>
+      </c>
+      <c r="I2167">
+        <f t="shared" si="91"/>
+        <v>2165</v>
+      </c>
+      <c r="J2167">
+        <f>SUM($F$3:F2167)/I2167</f>
+        <v>1.1436495565819851</v>
+      </c>
+      <c r="K2167">
+        <f t="shared" si="90"/>
+        <v>1.7401885599999998</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2168" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B2168">
+        <v>2014.54</v>
+      </c>
+      <c r="C2168">
+        <v>2028.65</v>
+      </c>
+      <c r="D2168">
+        <v>2012.59</v>
+      </c>
+      <c r="E2168">
+        <v>2016.57</v>
+      </c>
+      <c r="F2168">
+        <f t="shared" si="89"/>
+        <v>2.0165699999999998</v>
+      </c>
+      <c r="G2168">
+        <v>275372310</v>
+      </c>
+      <c r="H2168" s="3">
+        <v>469348000000</v>
+      </c>
+      <c r="I2168">
+        <f t="shared" si="91"/>
+        <v>2166</v>
+      </c>
+      <c r="J2168">
+        <f>SUM($F$3:F2168)/I2168</f>
+        <v>1.1440525669436739</v>
+      </c>
+      <c r="K2168">
+        <f t="shared" si="90"/>
+        <v>1.7426949199999997</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2169" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B2169">
+        <v>2002.16</v>
+      </c>
+      <c r="C2169">
+        <v>2031.57</v>
+      </c>
+      <c r="D2169">
+        <v>1988.01</v>
+      </c>
+      <c r="E2169">
+        <v>2010.85</v>
+      </c>
+      <c r="F2169">
+        <f t="shared" si="89"/>
+        <v>2.01085</v>
+      </c>
+      <c r="G2169">
+        <v>271850582</v>
+      </c>
+      <c r="H2169" s="3">
+        <v>464128000000</v>
+      </c>
+      <c r="I2169">
+        <f t="shared" si="91"/>
+        <v>2167</v>
+      </c>
+      <c r="J2169">
+        <f>SUM($F$3:F2169)/I2169</f>
+        <v>1.1444525657591129</v>
+      </c>
+      <c r="K2169">
+        <f t="shared" si="90"/>
+        <v>1.7449704399999995</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2170" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B2170">
+        <v>2039.85</v>
+      </c>
+      <c r="C2170">
+        <v>2057.81</v>
+      </c>
+      <c r="D2170">
+        <v>2035.25</v>
+      </c>
+      <c r="E2170">
+        <v>2057.81</v>
+      </c>
+      <c r="F2170">
+        <f t="shared" si="89"/>
+        <v>2.0578099999999999</v>
+      </c>
+      <c r="G2170">
+        <v>303552561</v>
+      </c>
+      <c r="H2170" s="3">
+        <v>531468000000</v>
+      </c>
+      <c r="I2170">
+        <f t="shared" si="91"/>
+        <v>2168</v>
+      </c>
+      <c r="J2170">
+        <f>SUM($F$3:F2170)/I2170</f>
+        <v>1.1448738560885598</v>
+      </c>
+      <c r="K2170">
+        <f t="shared" si="90"/>
+        <v>1.7472462399999997</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2171" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B2171">
+        <v>2062.9499999999998</v>
+      </c>
+      <c r="C2171">
+        <v>2080</v>
+      </c>
+      <c r="D2171">
+        <v>2055.69</v>
+      </c>
+      <c r="E2171">
+        <v>2071.7800000000002</v>
+      </c>
+      <c r="F2171">
+        <f t="shared" si="89"/>
+        <v>2.0717800000000004</v>
+      </c>
+      <c r="G2171">
+        <v>329718214</v>
+      </c>
+      <c r="H2171" s="3">
+        <v>567990000000</v>
+      </c>
+      <c r="I2171">
+        <f t="shared" si="91"/>
+        <v>2169</v>
+      </c>
+      <c r="J2171">
+        <f>SUM($F$3:F2171)/I2171</f>
+        <v>1.1453011987090815</v>
+      </c>
+      <c r="K2171">
+        <f t="shared" si="90"/>
+        <v>1.7494588799999995</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2172" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B2172">
+        <v>2070.1</v>
+      </c>
+      <c r="C2172">
+        <v>2073.9299999999998</v>
+      </c>
+      <c r="D2172">
+        <v>2057.2199999999998</v>
+      </c>
+      <c r="E2172">
+        <v>2057.38</v>
+      </c>
+      <c r="F2172">
+        <f t="shared" si="89"/>
+        <v>2.0573800000000002</v>
+      </c>
+      <c r="G2172">
+        <v>294184463</v>
+      </c>
+      <c r="H2172" s="3">
+        <v>490272000000</v>
+      </c>
+      <c r="I2172">
+        <f t="shared" si="91"/>
+        <v>2170</v>
+      </c>
+      <c r="J2172">
+        <f>SUM($F$3:F2172)/I2172</f>
+        <v>1.1457215115207364</v>
+      </c>
+      <c r="K2172">
+        <f t="shared" si="90"/>
+        <v>1.7513786799999997</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2173" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B2173">
+        <v>2061.27</v>
+      </c>
+      <c r="C2173">
+        <v>2073.7800000000002</v>
+      </c>
+      <c r="D2173">
+        <v>2043.41</v>
+      </c>
+      <c r="E2173">
+        <v>2063.21</v>
+      </c>
+      <c r="F2173">
+        <f t="shared" si="89"/>
+        <v>2.0632100000000002</v>
+      </c>
+      <c r="G2173">
+        <v>294318329</v>
+      </c>
+      <c r="H2173" s="3">
+        <v>536205000000</v>
+      </c>
+      <c r="I2173">
+        <f t="shared" si="91"/>
+        <v>2171</v>
+      </c>
+      <c r="J2173">
+        <f>SUM($F$3:F2173)/I2173</f>
+        <v>1.1461441225241813</v>
+      </c>
+      <c r="K2173">
+        <f t="shared" si="90"/>
+        <v>1.7533447999999998</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2174" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B2174">
+        <v>2058.58</v>
+      </c>
+      <c r="C2174">
+        <v>2080.3000000000002</v>
+      </c>
+      <c r="D2174">
+        <v>2049.96</v>
+      </c>
+      <c r="E2174">
+        <v>2050.52</v>
+      </c>
+      <c r="F2174">
+        <f t="shared" si="89"/>
+        <v>2.0505200000000001</v>
+      </c>
+      <c r="G2174">
+        <v>277338033</v>
+      </c>
+      <c r="H2174" s="3">
+        <v>491833000000</v>
+      </c>
+      <c r="I2174">
+        <f t="shared" si="91"/>
+        <v>2172</v>
+      </c>
+      <c r="J2174">
+        <f>SUM($F$3:F2174)/I2174</f>
+        <v>1.1465605018416194</v>
+      </c>
+      <c r="K2174">
+        <f t="shared" si="90"/>
+        <v>1.7551590799999999</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2175" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B2175">
+        <v>2069.7199999999998</v>
+      </c>
+      <c r="C2175">
+        <v>2070.73</v>
+      </c>
+      <c r="D2175">
+        <v>2037.57</v>
+      </c>
+      <c r="E2175">
+        <v>2050.37</v>
+      </c>
+      <c r="F2175">
+        <f t="shared" si="89"/>
+        <v>2.05037</v>
+      </c>
+      <c r="G2175">
+        <v>300248033</v>
+      </c>
+      <c r="H2175" s="3">
+        <v>519661000000</v>
+      </c>
+      <c r="I2175">
+        <f t="shared" si="91"/>
+        <v>2173</v>
+      </c>
+      <c r="J2175">
+        <f>SUM($F$3:F2175)/I2175</f>
+        <v>1.146976428900137</v>
+      </c>
+      <c r="K2175">
+        <f t="shared" si="90"/>
+        <v>1.7570399599999995</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2176" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B2176">
+        <v>2052.8200000000002</v>
+      </c>
+      <c r="C2176">
+        <v>2065.35</v>
+      </c>
+      <c r="D2176">
+        <v>2049.06</v>
+      </c>
+      <c r="E2176">
+        <v>2061.81</v>
+      </c>
+      <c r="F2176">
+        <f t="shared" si="89"/>
+        <v>2.0618099999999999</v>
+      </c>
+      <c r="G2176">
+        <v>309227330</v>
+      </c>
+      <c r="H2176" s="3">
+        <v>498030000000</v>
+      </c>
+      <c r="I2176">
+        <f t="shared" si="91"/>
+        <v>2174</v>
+      </c>
+      <c r="J2176">
+        <f>SUM($F$3:F2176)/I2176</f>
+        <v>1.1473972355105786</v>
+      </c>
+      <c r="K2176">
+        <f t="shared" si="90"/>
+        <v>1.7588393199999997</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2177" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B2177">
+        <v>2064.63</v>
+      </c>
+      <c r="C2177">
+        <v>2068.29</v>
+      </c>
+      <c r="D2177">
+        <v>2055.64</v>
+      </c>
+      <c r="E2177">
+        <v>2065.94</v>
+      </c>
+      <c r="F2177">
+        <f t="shared" si="89"/>
+        <v>2.0659399999999999</v>
+      </c>
+      <c r="G2177">
+        <v>294777283</v>
+      </c>
+      <c r="H2177" s="3">
+        <v>529819000000</v>
+      </c>
+      <c r="I2177">
+        <f t="shared" si="91"/>
+        <v>2175</v>
+      </c>
+      <c r="J2177">
+        <f>SUM($F$3:F2177)/I2177</f>
+        <v>1.1478195540229874</v>
+      </c>
+      <c r="K2177">
+        <f t="shared" si="90"/>
+        <v>1.7605544399999997</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2178" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B2178">
+        <v>2060.0500000000002</v>
+      </c>
+      <c r="C2178">
+        <v>2087.19</v>
+      </c>
+      <c r="D2178">
+        <v>2057.65</v>
+      </c>
+      <c r="E2178">
+        <v>2087.19</v>
+      </c>
+      <c r="F2178">
+        <f t="shared" ref="F2178" si="92">E2178/1000</f>
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="G2178">
+        <v>314303052</v>
+      </c>
+      <c r="H2178" s="3">
+        <v>571074000000</v>
+      </c>
+      <c r="I2178">
+        <f t="shared" si="91"/>
+        <v>2176</v>
+      </c>
+      <c r="J2178">
+        <f>SUM($F$3:F2178)/I2178</f>
+        <v>1.1482512499999991</v>
+      </c>
+      <c r="K2178">
+        <f t="shared" si="90"/>
+        <v>1.7625963599999996</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2178"/>
+  <dimension ref="A1:K2199"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -74353,7 +74353,7 @@
         <v>1571.68</v>
       </c>
       <c r="F1923">
-        <f t="shared" ref="F1923:F2177" si="89">E1923/1000</f>
+        <f t="shared" ref="F1923:F2176" si="89">E1923/1000</f>
         <v>1.57168</v>
       </c>
       <c r="G1923">
@@ -81313,7 +81313,7 @@
         <v>1.119025302525011</v>
       </c>
       <c r="K2101">
-        <f t="shared" ref="K2101:K2178" si="90">SUM(F1852:F2101)/250</f>
+        <f t="shared" ref="K2101:K2163" si="90">SUM(F1852:F2101)/250</f>
         <v>1.6052981200000014</v>
       </c>
     </row>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2178" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2199" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -83737,29 +83737,29 @@
     </row>
     <row r="2164" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2164" s="1">
-        <v>46080</v>
+        <v>46055</v>
       </c>
       <c r="B2164">
-        <v>2060.0500000000002</v>
+        <v>2023.78</v>
       </c>
       <c r="C2164">
-        <v>2087.19</v>
+        <v>2042.56</v>
       </c>
       <c r="D2164">
-        <v>2057.65</v>
+        <v>1992.38</v>
       </c>
       <c r="E2164">
-        <v>2087.19</v>
+        <v>1992.38</v>
       </c>
       <c r="F2164">
         <f t="shared" si="89"/>
-        <v>2.0871900000000001</v>
+        <v>1.99238</v>
       </c>
       <c r="G2164">
-        <v>314303052</v>
+        <v>326813703</v>
       </c>
       <c r="H2164" s="3">
-        <v>571074000000</v>
+        <v>571826000000</v>
       </c>
       <c r="I2164">
         <f t="shared" si="91"/>
@@ -83767,38 +83767,38 @@
       </c>
       <c r="J2164">
         <f>SUM($F$3:F2164)/I2164</f>
-        <v>1.1424320027752071</v>
+        <v>1.1423881498612385</v>
       </c>
       <c r="K2164">
-        <f t="shared" si="90"/>
-        <v>1.7324908400000001</v>
+        <f>SUM(F1915:F2164)/250</f>
+        <v>1.7321116000000001</v>
       </c>
     </row>
     <row r="2165" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2165" s="1">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B2165">
-        <v>2023.78</v>
+        <v>2011.79</v>
       </c>
       <c r="C2165">
-        <v>2042.56</v>
+        <v>2041.13</v>
       </c>
       <c r="D2165">
-        <v>1992.38</v>
+        <v>2003.77</v>
       </c>
       <c r="E2165">
-        <v>1992.38</v>
+        <v>2041.13</v>
       </c>
       <c r="F2165">
         <f t="shared" si="89"/>
-        <v>1.99238</v>
+        <v>2.0411299999999999</v>
       </c>
       <c r="G2165">
-        <v>326813703</v>
+        <v>326584324</v>
       </c>
       <c r="H2165" s="3">
-        <v>571826000000</v>
+        <v>596548000000</v>
       </c>
       <c r="I2165">
         <f t="shared" si="91"/>
@@ -83806,38 +83806,38 @@
       </c>
       <c r="J2165">
         <f>SUM($F$3:F2165)/I2165</f>
-        <v>1.1428249514563096</v>
+        <v>1.1428036569579276</v>
       </c>
       <c r="K2165">
-        <f t="shared" si="90"/>
-        <v>1.7349923200000001</v>
+        <f t="shared" ref="K2165:K2199" si="92">SUM(F1916:F2165)/250</f>
+        <v>1.7348080800000001</v>
       </c>
     </row>
     <row r="2166" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2166" s="1">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B2166">
-        <v>2011.79</v>
+        <v>2032.12</v>
       </c>
       <c r="C2166">
-        <v>2041.13</v>
+        <v>2036.38</v>
       </c>
       <c r="D2166">
-        <v>2003.77</v>
+        <v>2008.37</v>
       </c>
       <c r="E2166">
-        <v>2041.13</v>
+        <v>2029.79</v>
       </c>
       <c r="F2166">
         <f t="shared" si="89"/>
-        <v>2.0411299999999999</v>
+        <v>2.0297899999999998</v>
       </c>
       <c r="G2166">
-        <v>326584324</v>
+        <v>321148922</v>
       </c>
       <c r="H2166" s="3">
-        <v>596548000000</v>
+        <v>559149000000</v>
       </c>
       <c r="I2166">
         <f t="shared" si="91"/>
@@ -83845,38 +83845,38 @@
       </c>
       <c r="J2166">
         <f>SUM($F$3:F2166)/I2166</f>
-        <v>1.1432400646950083</v>
+        <v>1.1432135397412189</v>
       </c>
       <c r="K2166">
-        <f t="shared" si="90"/>
-        <v>1.7376932000000003</v>
+        <f t="shared" si="92"/>
+        <v>1.7374636000000001</v>
       </c>
     </row>
     <row r="2167" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2167" s="1">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B2167">
-        <v>2032.12</v>
+        <v>2014.54</v>
       </c>
       <c r="C2167">
-        <v>2036.38</v>
+        <v>2028.65</v>
       </c>
       <c r="D2167">
-        <v>2008.37</v>
+        <v>2012.59</v>
       </c>
       <c r="E2167">
-        <v>2029.79</v>
+        <v>2016.57</v>
       </c>
       <c r="F2167">
         <f t="shared" si="89"/>
-        <v>2.0297899999999998</v>
+        <v>2.0165699999999998</v>
       </c>
       <c r="G2167">
-        <v>321148922</v>
+        <v>275372310</v>
       </c>
       <c r="H2167" s="3">
-        <v>559149000000</v>
+        <v>469348000000</v>
       </c>
       <c r="I2167">
         <f t="shared" si="91"/>
@@ -83884,38 +83884,38 @@
       </c>
       <c r="J2167">
         <f>SUM($F$3:F2167)/I2167</f>
-        <v>1.1436495565819851</v>
+        <v>1.1436169376443406</v>
       </c>
       <c r="K2167">
-        <f t="shared" si="90"/>
-        <v>1.7401885599999998</v>
+        <f t="shared" si="92"/>
+        <v>1.7399060799999997</v>
       </c>
     </row>
     <row r="2168" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2168" s="1">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B2168">
-        <v>2014.54</v>
+        <v>2002.16</v>
       </c>
       <c r="C2168">
-        <v>2028.65</v>
+        <v>2031.57</v>
       </c>
       <c r="D2168">
-        <v>2012.59</v>
+        <v>1988.01</v>
       </c>
       <c r="E2168">
-        <v>2016.57</v>
+        <v>2010.85</v>
       </c>
       <c r="F2168">
         <f t="shared" si="89"/>
-        <v>2.0165699999999998</v>
+        <v>2.01085</v>
       </c>
       <c r="G2168">
-        <v>275372310</v>
+        <v>271850582</v>
       </c>
       <c r="H2168" s="3">
-        <v>469348000000</v>
+        <v>464128000000</v>
       </c>
       <c r="I2168">
         <f t="shared" si="91"/>
@@ -83923,38 +83923,38 @@
       </c>
       <c r="J2168">
         <f>SUM($F$3:F2168)/I2168</f>
-        <v>1.1440525669436739</v>
+        <v>1.1440173222529999</v>
       </c>
       <c r="K2168">
-        <f t="shared" si="90"/>
-        <v>1.7426949199999997</v>
+        <f t="shared" si="92"/>
+        <v>1.7423895599999997</v>
       </c>
     </row>
     <row r="2169" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2169" s="1">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B2169">
-        <v>2002.16</v>
+        <v>2039.85</v>
       </c>
       <c r="C2169">
-        <v>2031.57</v>
+        <v>2057.81</v>
       </c>
       <c r="D2169">
-        <v>1988.01</v>
+        <v>2035.25</v>
       </c>
       <c r="E2169">
-        <v>2010.85</v>
+        <v>2057.81</v>
       </c>
       <c r="F2169">
         <f t="shared" si="89"/>
-        <v>2.01085</v>
+        <v>2.0578099999999999</v>
       </c>
       <c r="G2169">
-        <v>271850582</v>
+        <v>303552561</v>
       </c>
       <c r="H2169" s="3">
-        <v>464128000000</v>
+        <v>531468000000</v>
       </c>
       <c r="I2169">
         <f t="shared" si="91"/>
@@ -83962,38 +83962,38 @@
       </c>
       <c r="J2169">
         <f>SUM($F$3:F2169)/I2169</f>
-        <v>1.1444525657591129</v>
+        <v>1.1444390078449458</v>
       </c>
       <c r="K2169">
-        <f t="shared" si="90"/>
-        <v>1.7449704399999995</v>
+        <f t="shared" si="92"/>
+        <v>1.7448529199999994</v>
       </c>
     </row>
     <row r="2170" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2170" s="1">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B2170">
-        <v>2039.85</v>
+        <v>2062.9499999999998</v>
       </c>
       <c r="C2170">
-        <v>2057.81</v>
+        <v>2080</v>
       </c>
       <c r="D2170">
-        <v>2035.25</v>
+        <v>2055.69</v>
       </c>
       <c r="E2170">
-        <v>2057.81</v>
+        <v>2071.7800000000002</v>
       </c>
       <c r="F2170">
         <f t="shared" si="89"/>
-        <v>2.0578099999999999</v>
+        <v>2.0717800000000004</v>
       </c>
       <c r="G2170">
-        <v>303552561</v>
+        <v>329718214</v>
       </c>
       <c r="H2170" s="3">
-        <v>531468000000</v>
+        <v>567990000000</v>
       </c>
       <c r="I2170">
         <f t="shared" si="91"/>
@@ -84001,38 +84001,38 @@
       </c>
       <c r="J2170">
         <f>SUM($F$3:F2170)/I2170</f>
-        <v>1.1448738560885598</v>
+        <v>1.1448667481549804</v>
       </c>
       <c r="K2170">
-        <f t="shared" si="90"/>
-        <v>1.7472462399999997</v>
+        <f t="shared" si="92"/>
+        <v>1.7471845999999995</v>
       </c>
     </row>
     <row r="2171" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2171" s="1">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B2171">
-        <v>2062.9499999999998</v>
+        <v>2070.1</v>
       </c>
       <c r="C2171">
-        <v>2080</v>
+        <v>2073.9299999999998</v>
       </c>
       <c r="D2171">
-        <v>2055.69</v>
+        <v>2057.2199999999998</v>
       </c>
       <c r="E2171">
-        <v>2071.7800000000002</v>
+        <v>2057.38</v>
       </c>
       <c r="F2171">
         <f t="shared" si="89"/>
-        <v>2.0717800000000004</v>
+        <v>2.0573800000000002</v>
       </c>
       <c r="G2171">
-        <v>329718214</v>
+        <v>294184463</v>
       </c>
       <c r="H2171" s="3">
-        <v>567990000000</v>
+        <v>490272000000</v>
       </c>
       <c r="I2171">
         <f t="shared" si="91"/>
@@ -84040,38 +84040,38 @@
       </c>
       <c r="J2171">
         <f>SUM($F$3:F2171)/I2171</f>
-        <v>1.1453011987090815</v>
+        <v>1.1452874550484085</v>
       </c>
       <c r="K2171">
-        <f t="shared" si="90"/>
-        <v>1.7494588799999995</v>
+        <f t="shared" si="92"/>
+        <v>1.7493396399999994</v>
       </c>
     </row>
     <row r="2172" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2172" s="1">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B2172">
-        <v>2070.1</v>
+        <v>2061.27</v>
       </c>
       <c r="C2172">
-        <v>2073.9299999999998</v>
+        <v>2073.7800000000002</v>
       </c>
       <c r="D2172">
-        <v>2057.2199999999998</v>
+        <v>2043.41</v>
       </c>
       <c r="E2172">
-        <v>2057.38</v>
+        <v>2063.21</v>
       </c>
       <c r="F2172">
         <f t="shared" si="89"/>
-        <v>2.0573800000000002</v>
+        <v>2.0632100000000002</v>
       </c>
       <c r="G2172">
-        <v>294184463</v>
+        <v>294318329</v>
       </c>
       <c r="H2172" s="3">
-        <v>490272000000</v>
+        <v>536205000000</v>
       </c>
       <c r="I2172">
         <f t="shared" si="91"/>
@@ -84079,38 +84079,38 @@
       </c>
       <c r="J2172">
         <f>SUM($F$3:F2172)/I2172</f>
-        <v>1.1457215115207364</v>
+        <v>1.1457104608294919</v>
       </c>
       <c r="K2172">
-        <f t="shared" si="90"/>
-        <v>1.7513786799999997</v>
+        <f t="shared" si="92"/>
+        <v>1.7512827599999998</v>
       </c>
     </row>
     <row r="2173" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2173" s="1">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B2173">
-        <v>2061.27</v>
+        <v>2058.58</v>
       </c>
       <c r="C2173">
-        <v>2073.7800000000002</v>
+        <v>2080.3000000000002</v>
       </c>
       <c r="D2173">
-        <v>2043.41</v>
+        <v>2049.96</v>
       </c>
       <c r="E2173">
-        <v>2063.21</v>
+        <v>2050.52</v>
       </c>
       <c r="F2173">
         <f t="shared" si="89"/>
-        <v>2.0632100000000002</v>
+        <v>2.0505200000000001</v>
       </c>
       <c r="G2173">
-        <v>294318329</v>
+        <v>277338033</v>
       </c>
       <c r="H2173" s="3">
-        <v>536205000000</v>
+        <v>491833000000</v>
       </c>
       <c r="I2173">
         <f t="shared" si="91"/>
@@ -84118,38 +84118,38 @@
       </c>
       <c r="J2173">
         <f>SUM($F$3:F2173)/I2173</f>
-        <v>1.1461441225241813</v>
+        <v>1.146127231690464</v>
       </c>
       <c r="K2173">
-        <f t="shared" si="90"/>
-        <v>1.7533447999999998</v>
+        <f t="shared" si="92"/>
+        <v>1.7531981199999997</v>
       </c>
     </row>
     <row r="2174" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2174" s="1">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="B2174">
-        <v>2058.58</v>
+        <v>2069.7199999999998</v>
       </c>
       <c r="C2174">
-        <v>2080.3000000000002</v>
+        <v>2070.73</v>
       </c>
       <c r="D2174">
-        <v>2049.96</v>
+        <v>2037.57</v>
       </c>
       <c r="E2174">
-        <v>2050.52</v>
+        <v>2050.37</v>
       </c>
       <c r="F2174">
         <f t="shared" si="89"/>
-        <v>2.0505200000000001</v>
+        <v>2.05037</v>
       </c>
       <c r="G2174">
-        <v>277338033</v>
+        <v>300248033</v>
       </c>
       <c r="H2174" s="3">
-        <v>491833000000</v>
+        <v>519661000000</v>
       </c>
       <c r="I2174">
         <f t="shared" si="91"/>
@@ -84157,38 +84157,38 @@
       </c>
       <c r="J2174">
         <f>SUM($F$3:F2174)/I2174</f>
-        <v>1.1465605018416194</v>
+        <v>1.1465435497237557</v>
       </c>
       <c r="K2174">
-        <f t="shared" si="90"/>
-        <v>1.7551590799999999</v>
+        <f t="shared" si="92"/>
+        <v>1.7550117999999997</v>
       </c>
     </row>
     <row r="2175" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2175" s="1">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B2175">
-        <v>2069.7199999999998</v>
+        <v>2052.8200000000002</v>
       </c>
       <c r="C2175">
-        <v>2070.73</v>
+        <v>2065.35</v>
       </c>
       <c r="D2175">
-        <v>2037.57</v>
+        <v>2049.06</v>
       </c>
       <c r="E2175">
-        <v>2050.37</v>
+        <v>2061.81</v>
       </c>
       <c r="F2175">
         <f t="shared" si="89"/>
-        <v>2.05037</v>
+        <v>2.0618099999999999</v>
       </c>
       <c r="G2175">
-        <v>300248033</v>
+        <v>309227330</v>
       </c>
       <c r="H2175" s="3">
-        <v>519661000000</v>
+        <v>498030000000</v>
       </c>
       <c r="I2175">
         <f t="shared" si="91"/>
@@ -84196,38 +84196,38 @@
       </c>
       <c r="J2175">
         <f>SUM($F$3:F2175)/I2175</f>
-        <v>1.146976428900137</v>
+        <v>1.1469647491946606</v>
       </c>
       <c r="K2175">
-        <f t="shared" si="90"/>
-        <v>1.7570399599999995</v>
+        <f t="shared" si="92"/>
+        <v>1.7569384399999994</v>
       </c>
     </row>
     <row r="2176" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2176" s="1">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B2176">
-        <v>2052.8200000000002</v>
+        <v>2064.63</v>
       </c>
       <c r="C2176">
-        <v>2065.35</v>
+        <v>2068.29</v>
       </c>
       <c r="D2176">
-        <v>2049.06</v>
+        <v>2055.64</v>
       </c>
       <c r="E2176">
-        <v>2061.81</v>
+        <v>2065.94</v>
       </c>
       <c r="F2176">
         <f t="shared" si="89"/>
-        <v>2.0618099999999999</v>
+        <v>2.0659399999999999</v>
       </c>
       <c r="G2176">
-        <v>309227330</v>
+        <v>294777283</v>
       </c>
       <c r="H2176" s="3">
-        <v>498030000000</v>
+        <v>529819000000</v>
       </c>
       <c r="I2176">
         <f t="shared" si="91"/>
@@ -84235,38 +84235,38 @@
       </c>
       <c r="J2176">
         <f>SUM($F$3:F2176)/I2176</f>
-        <v>1.1473972355105786</v>
+        <v>1.1473874609015629</v>
       </c>
       <c r="K2176">
-        <f t="shared" si="90"/>
-        <v>1.7588393199999997</v>
+        <f t="shared" si="92"/>
+        <v>1.7587543199999995</v>
       </c>
     </row>
     <row r="2177" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2177" s="1">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B2177">
-        <v>2064.63</v>
+        <v>2060.0500000000002</v>
       </c>
       <c r="C2177">
-        <v>2068.29</v>
+        <v>2087.19</v>
       </c>
       <c r="D2177">
-        <v>2055.64</v>
+        <v>2057.65</v>
       </c>
       <c r="E2177">
-        <v>2065.94</v>
+        <v>2087.19</v>
       </c>
       <c r="F2177">
-        <f t="shared" si="89"/>
-        <v>2.0659399999999999</v>
+        <f t="shared" ref="F2177:F2199" si="93">E2177/1000</f>
+        <v>2.0871900000000001</v>
       </c>
       <c r="G2177">
-        <v>294777283</v>
+        <v>314303052</v>
       </c>
       <c r="H2177" s="3">
-        <v>529819000000</v>
+        <v>571074000000</v>
       </c>
       <c r="I2177">
         <f t="shared" si="91"/>
@@ -84277,35 +84277,35 @@
         <v>1.1478195540229874</v>
       </c>
       <c r="K2177">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>1.7605544399999997</v>
       </c>
     </row>
     <row r="2178" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2178" s="1">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B2178">
-        <v>2060.0500000000002</v>
+        <v>2054.84</v>
       </c>
       <c r="C2178">
-        <v>2087.19</v>
+        <v>2066.84</v>
       </c>
       <c r="D2178">
-        <v>2057.65</v>
+        <v>2022</v>
       </c>
       <c r="E2178">
-        <v>2087.19</v>
+        <v>2033.9</v>
       </c>
       <c r="F2178">
-        <f t="shared" ref="F2178" si="92">E2178/1000</f>
-        <v>2.0871900000000001</v>
+        <f t="shared" si="93"/>
+        <v>2.0339</v>
       </c>
       <c r="G2178">
-        <v>314303052</v>
+        <v>358236827</v>
       </c>
       <c r="H2178" s="3">
-        <v>571074000000</v>
+        <v>621437000000</v>
       </c>
       <c r="I2178">
         <f t="shared" si="91"/>
@@ -84313,11 +84313,830 @@
       </c>
       <c r="J2178">
         <f>SUM($F$3:F2178)/I2178</f>
-        <v>1.1482512499999991</v>
+        <v>1.1482267601102929</v>
       </c>
       <c r="K2178">
-        <f t="shared" si="90"/>
-        <v>1.7625963599999996</v>
+        <f t="shared" si="92"/>
+        <v>1.7623831999999995</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2179" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B2179">
+        <v>2036.52</v>
+      </c>
+      <c r="C2179">
+        <v>2040.31</v>
+      </c>
+      <c r="D2179">
+        <v>1946.62</v>
+      </c>
+      <c r="E2179">
+        <v>1948.74</v>
+      </c>
+      <c r="F2179">
+        <f t="shared" si="93"/>
+        <v>1.9487399999999999</v>
+      </c>
+      <c r="G2179">
+        <v>366179310</v>
+      </c>
+      <c r="H2179" s="3">
+        <v>638598000000</v>
+      </c>
+      <c r="I2179">
+        <f t="shared" si="91"/>
+        <v>2177</v>
+      </c>
+      <c r="J2179">
+        <f>SUM($F$3:F2179)/I2179</f>
+        <v>1.1485944740468523</v>
+      </c>
+      <c r="K2179">
+        <f t="shared" si="92"/>
+        <v>1.7636799999999997</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2180" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B2180">
+        <v>1926.55</v>
+      </c>
+      <c r="C2180">
+        <v>1962.64</v>
+      </c>
+      <c r="D2180">
+        <v>1926.55</v>
+      </c>
+      <c r="E2180">
+        <v>1941.18</v>
+      </c>
+      <c r="F2180">
+        <f t="shared" si="93"/>
+        <v>1.9411800000000001</v>
+      </c>
+      <c r="G2180">
+        <v>279455229</v>
+      </c>
+      <c r="H2180" s="3">
+        <v>453365000000</v>
+      </c>
+      <c r="I2180">
+        <f t="shared" si="91"/>
+        <v>2178</v>
+      </c>
+      <c r="J2180">
+        <f>SUM($F$3:F2180)/I2180</f>
+        <v>1.1489583792470144</v>
+      </c>
+      <c r="K2180">
+        <f t="shared" si="92"/>
+        <v>1.7648915199999997</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2181" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B2181">
+        <v>1975.39</v>
+      </c>
+      <c r="C2181">
+        <v>1984.96</v>
+      </c>
+      <c r="D2181">
+        <v>1961.31</v>
+      </c>
+      <c r="E2181">
+        <v>1970.63</v>
+      </c>
+      <c r="F2181">
+        <f t="shared" si="93"/>
+        <v>1.9706300000000001</v>
+      </c>
+      <c r="G2181">
+        <v>307115415</v>
+      </c>
+      <c r="H2181" s="3">
+        <v>493162000000</v>
+      </c>
+      <c r="I2181">
+        <f t="shared" si="91"/>
+        <v>2179</v>
+      </c>
+      <c r="J2181">
+        <f>SUM($F$3:F2181)/I2181</f>
+        <v>1.1493354658100032</v>
+      </c>
+      <c r="K2181">
+        <f t="shared" si="92"/>
+        <v>1.7660673199999997</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2182" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B2182">
+        <v>1961.88</v>
+      </c>
+      <c r="C2182">
+        <v>2001.07</v>
+      </c>
+      <c r="D2182">
+        <v>1961.23</v>
+      </c>
+      <c r="E2182">
+        <v>2001.07</v>
+      </c>
+      <c r="F2182">
+        <f t="shared" si="93"/>
+        <v>2.0010699999999999</v>
+      </c>
+      <c r="G2182">
+        <v>290684649</v>
+      </c>
+      <c r="H2182" s="3">
+        <v>453876000000</v>
+      </c>
+      <c r="I2182">
+        <f t="shared" si="91"/>
+        <v>2180</v>
+      </c>
+      <c r="J2182">
+        <f>SUM($F$3:F2182)/I2182</f>
+        <v>1.1497261697247692</v>
+      </c>
+      <c r="K2182">
+        <f t="shared" si="92"/>
+        <v>1.7673977999999999</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2183" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B2183">
+        <v>1971.41</v>
+      </c>
+      <c r="C2183">
+        <v>2008.1</v>
+      </c>
+      <c r="D2183">
+        <v>1950.91</v>
+      </c>
+      <c r="E2183">
+        <v>2002.92</v>
+      </c>
+      <c r="F2183">
+        <f t="shared" si="93"/>
+        <v>2.00292</v>
+      </c>
+      <c r="G2183">
+        <v>353015944</v>
+      </c>
+      <c r="H2183" s="3">
+        <v>578329000000</v>
+      </c>
+      <c r="I2183">
+        <f t="shared" si="91"/>
+        <v>2181</v>
+      </c>
+      <c r="J2183">
+        <f>SUM($F$3:F2183)/I2183</f>
+        <v>1.1501173635946798</v>
+      </c>
+      <c r="K2183">
+        <f t="shared" si="92"/>
+        <v>1.7687814000000002</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2184" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B2184">
+        <v>2019.86</v>
+      </c>
+      <c r="C2184">
+        <v>2040.49</v>
+      </c>
+      <c r="D2184">
+        <v>2019.63</v>
+      </c>
+      <c r="E2184">
+        <v>2037.7</v>
+      </c>
+      <c r="F2184">
+        <f t="shared" si="93"/>
+        <v>2.0377000000000001</v>
+      </c>
+      <c r="G2184">
+        <v>332463509</v>
+      </c>
+      <c r="H2184" s="3">
+        <v>565058000000</v>
+      </c>
+      <c r="I2184">
+        <f t="shared" si="91"/>
+        <v>2182</v>
+      </c>
+      <c r="J2184">
+        <f>SUM($F$3:F2184)/I2184</f>
+        <v>1.1505241384051312</v>
+      </c>
+      <c r="K2184">
+        <f t="shared" si="92"/>
+        <v>1.7702129599999998</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2185" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B2185">
+        <v>2040.66</v>
+      </c>
+      <c r="C2185">
+        <v>2044.21</v>
+      </c>
+      <c r="D2185">
+        <v>2023.31</v>
+      </c>
+      <c r="E2185">
+        <v>2028.27</v>
+      </c>
+      <c r="F2185">
+        <f t="shared" si="93"/>
+        <v>2.02827</v>
+      </c>
+      <c r="G2185">
+        <v>331656983</v>
+      </c>
+      <c r="H2185" s="3">
+        <v>553128000000</v>
+      </c>
+      <c r="I2185">
+        <f t="shared" si="91"/>
+        <v>2183</v>
+      </c>
+      <c r="J2185">
+        <f>SUM($F$3:F2185)/I2185</f>
+        <v>1.1509262207970665</v>
+      </c>
+      <c r="K2185">
+        <f t="shared" si="92"/>
+        <v>1.7716653600000003</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2186" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B2186">
+        <v>2024.59</v>
+      </c>
+      <c r="C2186">
+        <v>2028.26</v>
+      </c>
+      <c r="D2186">
+        <v>1998.08</v>
+      </c>
+      <c r="E2186">
+        <v>2005.8</v>
+      </c>
+      <c r="F2186">
+        <f t="shared" si="93"/>
+        <v>2.0057999999999998</v>
+      </c>
+      <c r="G2186">
+        <v>345968408</v>
+      </c>
+      <c r="H2186" s="3">
+        <v>518572000000</v>
+      </c>
+      <c r="I2186">
+        <f t="shared" si="91"/>
+        <v>2184</v>
+      </c>
+      <c r="J2186">
+        <f>SUM($F$3:F2186)/I2186</f>
+        <v>1.1513176465201447</v>
+      </c>
+      <c r="K2186">
+        <f t="shared" si="92"/>
+        <v>1.7733637200000001</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2187" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2187">
+        <v>1997.87</v>
+      </c>
+      <c r="C2187">
+        <v>2004.11</v>
+      </c>
+      <c r="D2187">
+        <v>1971.4</v>
+      </c>
+      <c r="E2187">
+        <v>1975.8</v>
+      </c>
+      <c r="F2187">
+        <f t="shared" si="93"/>
+        <v>1.9758</v>
+      </c>
+      <c r="G2187">
+        <v>342108398</v>
+      </c>
+      <c r="H2187" s="3">
+        <v>498216000000</v>
+      </c>
+      <c r="I2187">
+        <f t="shared" si="91"/>
+        <v>2185</v>
+      </c>
+      <c r="J2187">
+        <f>SUM($F$3:F2187)/I2187</f>
+        <v>1.1516949839816917</v>
+      </c>
+      <c r="K2187">
+        <f t="shared" si="92"/>
+        <v>1.774915</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2188" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B2188">
+        <v>1973.62</v>
+      </c>
+      <c r="C2188">
+        <v>1984.4</v>
+      </c>
+      <c r="D2188">
+        <v>1959.13</v>
+      </c>
+      <c r="E2188">
+        <v>1984.4</v>
+      </c>
+      <c r="F2188">
+        <f t="shared" si="93"/>
+        <v>1.9844000000000002</v>
+      </c>
+      <c r="G2188">
+        <v>304564011</v>
+      </c>
+      <c r="H2188" s="3">
+        <v>452847000000</v>
+      </c>
+      <c r="I2188">
+        <f t="shared" si="91"/>
+        <v>2186</v>
+      </c>
+      <c r="J2188">
+        <f>SUM($F$3:F2188)/I2188</f>
+        <v>1.1520759103385161</v>
+      </c>
+      <c r="K2188">
+        <f t="shared" si="92"/>
+        <v>1.7763529599999999</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2189" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B2189">
+        <v>1987.58</v>
+      </c>
+      <c r="C2189">
+        <v>1988.4</v>
+      </c>
+      <c r="D2189">
+        <v>1944.32</v>
+      </c>
+      <c r="E2189">
+        <v>1944.56</v>
+      </c>
+      <c r="F2189">
+        <f t="shared" si="93"/>
+        <v>1.9445599999999998</v>
+      </c>
+      <c r="G2189">
+        <v>275484940</v>
+      </c>
+      <c r="H2189" s="3">
+        <v>421293000000</v>
+      </c>
+      <c r="I2189">
+        <f t="shared" si="91"/>
+        <v>2187</v>
+      </c>
+      <c r="J2189">
+        <f>SUM($F$3:F2189)/I2189</f>
+        <v>1.1524382716049364</v>
+      </c>
+      <c r="K2189">
+        <f t="shared" si="92"/>
+        <v>1.77756808</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2190" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B2190">
+        <v>1949.57</v>
+      </c>
+      <c r="C2190">
+        <v>1979.32</v>
+      </c>
+      <c r="D2190">
+        <v>1944.18</v>
+      </c>
+      <c r="E2190">
+        <v>1978.71</v>
+      </c>
+      <c r="F2190">
+        <f t="shared" si="93"/>
+        <v>1.97871</v>
+      </c>
+      <c r="G2190">
+        <v>260397356</v>
+      </c>
+      <c r="H2190" s="3">
+        <v>422286000000</v>
+      </c>
+      <c r="I2190">
+        <f t="shared" si="91"/>
+        <v>2188</v>
+      </c>
+      <c r="J2190">
+        <f>SUM($F$3:F2190)/I2190</f>
+        <v>1.1528159095063968</v>
+      </c>
+      <c r="K2190">
+        <f t="shared" si="92"/>
+        <v>1.77868016</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2191" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B2191">
+        <v>1953.4</v>
+      </c>
+      <c r="C2191">
+        <v>1960.67</v>
+      </c>
+      <c r="D2191">
+        <v>1929.5</v>
+      </c>
+      <c r="E2191">
+        <v>1936.5</v>
+      </c>
+      <c r="F2191">
+        <f t="shared" si="93"/>
+        <v>1.9365000000000001</v>
+      </c>
+      <c r="G2191">
+        <v>261962679</v>
+      </c>
+      <c r="H2191" s="3">
+        <v>425599000000</v>
+      </c>
+      <c r="I2191">
+        <f t="shared" si="91"/>
+        <v>2189</v>
+      </c>
+      <c r="J2191">
+        <f>SUM($F$3:F2191)/I2191</f>
+        <v>1.153173919597988</v>
+      </c>
+      <c r="K2191">
+        <f t="shared" si="92"/>
+        <v>1.7796935599999999</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2192" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B2192">
+        <v>1942.45</v>
+      </c>
+      <c r="C2192">
+        <v>1949.62</v>
+      </c>
+      <c r="D2192">
+        <v>1878.89</v>
+      </c>
+      <c r="E2192">
+        <v>1878.89</v>
+      </c>
+      <c r="F2192">
+        <f t="shared" si="93"/>
+        <v>1.8788900000000002</v>
+      </c>
+      <c r="G2192">
+        <v>286743719</v>
+      </c>
+      <c r="H2192" s="3">
+        <v>459391000000</v>
+      </c>
+      <c r="I2192">
+        <f t="shared" si="91"/>
+        <v>2190</v>
+      </c>
+      <c r="J2192">
+        <f>SUM($F$3:F2192)/I2192</f>
+        <v>1.153505296803651</v>
+      </c>
+      <c r="K2192">
+        <f t="shared" si="92"/>
+        <v>1.780497</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2193" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B2193">
+        <v>1844.26</v>
+      </c>
+      <c r="C2193">
+        <v>1851.2</v>
+      </c>
+      <c r="D2193">
+        <v>1762.94</v>
+      </c>
+      <c r="E2193">
+        <v>1773.68</v>
+      </c>
+      <c r="F2193">
+        <f t="shared" si="93"/>
+        <v>1.7736800000000001</v>
+      </c>
+      <c r="G2193">
+        <v>319895910</v>
+      </c>
+      <c r="H2193" s="3">
+        <v>467237000000</v>
+      </c>
+      <c r="I2193">
+        <f t="shared" si="91"/>
+        <v>2191</v>
+      </c>
+      <c r="J2193">
+        <f>SUM($F$3:F2193)/I2193</f>
+        <v>1.1537883523505228</v>
+      </c>
+      <c r="K2193">
+        <f t="shared" si="92"/>
+        <v>1.78087332</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2194" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B2194">
+        <v>1808.69</v>
+      </c>
+      <c r="C2194">
+        <v>1833.14</v>
+      </c>
+      <c r="D2194">
+        <v>1778.34</v>
+      </c>
+      <c r="E2194">
+        <v>1833.14</v>
+      </c>
+      <c r="F2194">
+        <f t="shared" si="93"/>
+        <v>1.83314</v>
+      </c>
+      <c r="G2194">
+        <v>267063466</v>
+      </c>
+      <c r="H2194" s="3">
+        <v>398046000000</v>
+      </c>
+      <c r="I2194">
+        <f t="shared" si="91"/>
+        <v>2192</v>
+      </c>
+      <c r="J2194">
+        <f>SUM($F$3:F2194)/I2194</f>
+        <v>1.1540982755474434</v>
+      </c>
+      <c r="K2194">
+        <f t="shared" si="92"/>
+        <v>1.7814226799999999</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2195" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B2195">
+        <v>1841.12</v>
+      </c>
+      <c r="C2195">
+        <v>1876.08</v>
+      </c>
+      <c r="D2195">
+        <v>1841.12</v>
+      </c>
+      <c r="E2195">
+        <v>1869.63</v>
+      </c>
+      <c r="F2195">
+        <f t="shared" si="93"/>
+        <v>1.8696300000000001</v>
+      </c>
+      <c r="G2195">
+        <v>266776082</v>
+      </c>
+      <c r="H2195" s="3">
+        <v>413658000000</v>
+      </c>
+      <c r="I2195">
+        <f t="shared" si="91"/>
+        <v>2193</v>
+      </c>
+      <c r="J2195">
+        <f>SUM($F$3:F2195)/I2195</f>
+        <v>1.1544245554035548</v>
+      </c>
+      <c r="K2195">
+        <f t="shared" si="92"/>
+        <v>1.78225568</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2196" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B2196">
+        <v>1868.31</v>
+      </c>
+      <c r="C2196">
+        <v>1876.66</v>
+      </c>
+      <c r="D2196">
+        <v>1825.52</v>
+      </c>
+      <c r="E2196">
+        <v>1831.78</v>
+      </c>
+      <c r="F2196">
+        <f t="shared" si="93"/>
+        <v>1.83178</v>
+      </c>
+      <c r="G2196">
+        <v>246904718</v>
+      </c>
+      <c r="H2196" s="3">
+        <v>361529000000</v>
+      </c>
+      <c r="I2196">
+        <f t="shared" si="91"/>
+        <v>2194</v>
+      </c>
+      <c r="J2196">
+        <f>SUM($F$3:F2196)/I2196</f>
+        <v>1.1547332862351849</v>
+      </c>
+      <c r="K2196">
+        <f t="shared" si="92"/>
+        <v>1.7828171599999998</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2197" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B2197">
+        <v>1809.83</v>
+      </c>
+      <c r="C2197">
+        <v>1859.23</v>
+      </c>
+      <c r="D2197">
+        <v>1808.75</v>
+      </c>
+      <c r="E2197">
+        <v>1853.94</v>
+      </c>
+      <c r="F2197">
+        <f t="shared" si="93"/>
+        <v>1.8539400000000001</v>
+      </c>
+      <c r="G2197">
+        <v>219376681</v>
+      </c>
+      <c r="H2197" s="3">
+        <v>319294000000</v>
+      </c>
+      <c r="I2197">
+        <f t="shared" si="91"/>
+        <v>2195</v>
+      </c>
+      <c r="J2197">
+        <f>SUM($F$3:F2197)/I2197</f>
+        <v>1.1550518314350777</v>
+      </c>
+      <c r="K2197">
+        <f t="shared" si="92"/>
+        <v>1.78344828</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2198" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B2198">
+        <v>1828.7</v>
+      </c>
+      <c r="C2198">
+        <v>1856.99</v>
+      </c>
+      <c r="D2198">
+        <v>1816.14</v>
+      </c>
+      <c r="E2198">
+        <v>1856.99</v>
+      </c>
+      <c r="F2198">
+        <f t="shared" si="93"/>
+        <v>1.8569899999999999</v>
+      </c>
+      <c r="G2198">
+        <v>226300083</v>
+      </c>
+      <c r="H2198" s="3">
+        <v>332984000000</v>
+      </c>
+      <c r="I2198">
+        <f t="shared" si="91"/>
+        <v>2196</v>
+      </c>
+      <c r="J2198">
+        <f>SUM($F$3:F2198)/I2198</f>
+        <v>1.1553714754098343</v>
+      </c>
+      <c r="K2198">
+        <f t="shared" si="92"/>
+        <v>1.7840578</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2199" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B2199">
+        <v>1854.86</v>
+      </c>
+      <c r="C2199">
+        <v>1875.81</v>
+      </c>
+      <c r="D2199">
+        <v>1833.83</v>
+      </c>
+      <c r="E2199">
+        <v>1834.35</v>
+      </c>
+      <c r="F2199">
+        <f t="shared" si="93"/>
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="G2199">
+        <v>235589677</v>
+      </c>
+      <c r="H2199" s="3">
+        <v>369213000000</v>
+      </c>
+      <c r="I2199">
+        <f t="shared" si="91"/>
+        <v>2197</v>
+      </c>
+      <c r="J2199">
+        <f>SUM($F$3:F2199)/I2199</f>
+        <v>1.1556805234410541</v>
+      </c>
+      <c r="K2199">
+        <f t="shared" si="92"/>
+        <v>1.7846445999999998</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2199"/>
+  <dimension ref="A1:K2220"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2199" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2220" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -83809,7 +83809,7 @@
         <v>1.1428036569579276</v>
       </c>
       <c r="K2165">
-        <f t="shared" ref="K2165:K2199" si="92">SUM(F1916:F2165)/250</f>
+        <f t="shared" ref="K2165:K2220" si="92">SUM(F1916:F2165)/250</f>
         <v>1.7348080800000001</v>
       </c>
     </row>
@@ -84259,7 +84259,7 @@
         <v>2087.19</v>
       </c>
       <c r="F2177">
-        <f t="shared" ref="F2177:F2199" si="93">E2177/1000</f>
+        <f t="shared" ref="F2177:F2220" si="93">E2177/1000</f>
         <v>2.0871900000000001</v>
       </c>
       <c r="G2177">
@@ -85137,6 +85137,825 @@
       <c r="K2199">
         <f t="shared" si="92"/>
         <v>1.7846445999999998</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2200" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B2200">
+        <v>1866.93</v>
+      </c>
+      <c r="C2200">
+        <v>1869.7</v>
+      </c>
+      <c r="D2200">
+        <v>1850.74</v>
+      </c>
+      <c r="E2200">
+        <v>1866.82</v>
+      </c>
+      <c r="F2200">
+        <f t="shared" si="93"/>
+        <v>1.8668199999999999</v>
+      </c>
+      <c r="G2200">
+        <v>238252619</v>
+      </c>
+      <c r="H2200" s="3">
+        <v>394351000000</v>
+      </c>
+      <c r="I2200">
+        <f t="shared" si="91"/>
+        <v>2198</v>
+      </c>
+      <c r="J2200">
+        <f>SUM($F$3:F2200)/I2200</f>
+        <v>1.1560040627843478</v>
+      </c>
+      <c r="K2200">
+        <f t="shared" si="92"/>
+        <v>1.7854003199999999</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2201" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B2201">
+        <v>1860.56</v>
+      </c>
+      <c r="C2201">
+        <v>1860.56</v>
+      </c>
+      <c r="D2201">
+        <v>1815.95</v>
+      </c>
+      <c r="E2201">
+        <v>1826.24</v>
+      </c>
+      <c r="F2201">
+        <f t="shared" si="93"/>
+        <v>1.8262400000000001</v>
+      </c>
+      <c r="G2201">
+        <v>224974226</v>
+      </c>
+      <c r="H2201" s="3">
+        <v>349513000000</v>
+      </c>
+      <c r="I2201">
+        <f t="shared" si="91"/>
+        <v>2199</v>
+      </c>
+      <c r="J2201">
+        <f>SUM($F$3:F2201)/I2201</f>
+        <v>1.1563088540245547</v>
+      </c>
+      <c r="K2201">
+        <f t="shared" si="92"/>
+        <v>1.7861601199999999</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2202" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B2202">
+        <v>1833.4</v>
+      </c>
+      <c r="C2202">
+        <v>1835.22</v>
+      </c>
+      <c r="D2202">
+        <v>1788.94</v>
+      </c>
+      <c r="E2202">
+        <v>1790.35</v>
+      </c>
+      <c r="F2202">
+        <f t="shared" si="93"/>
+        <v>1.7903499999999999</v>
+      </c>
+      <c r="G2202">
+        <v>206746418</v>
+      </c>
+      <c r="H2202" s="3">
+        <v>304083000000</v>
+      </c>
+      <c r="I2202">
+        <f t="shared" si="91"/>
+        <v>2200</v>
+      </c>
+      <c r="J2202">
+        <f>SUM($F$3:F2202)/I2202</f>
+        <v>1.1565970545454529</v>
+      </c>
+      <c r="K2202">
+        <f t="shared" si="92"/>
+        <v>1.7869274399999997</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2203" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B2203">
+        <v>1792.17</v>
+      </c>
+      <c r="C2203">
+        <v>1816.79</v>
+      </c>
+      <c r="D2203">
+        <v>1790.36</v>
+      </c>
+      <c r="E2203">
+        <v>1808.47</v>
+      </c>
+      <c r="F2203">
+        <f t="shared" si="93"/>
+        <v>1.80847</v>
+      </c>
+      <c r="G2203">
+        <v>187331319</v>
+      </c>
+      <c r="H2203" s="3">
+        <v>296016000000</v>
+      </c>
+      <c r="I2203">
+        <f t="shared" si="91"/>
+        <v>2201</v>
+      </c>
+      <c r="J2203">
+        <f>SUM($F$3:F2203)/I2203</f>
+        <v>1.1568932258064499</v>
+      </c>
+      <c r="K2203">
+        <f t="shared" si="92"/>
+        <v>1.7878681999999997</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2204" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B2204">
+        <v>1845.36</v>
+      </c>
+      <c r="C2204">
+        <v>1898.21</v>
+      </c>
+      <c r="D2204">
+        <v>1845.36</v>
+      </c>
+      <c r="E2204">
+        <v>1898.21</v>
+      </c>
+      <c r="F2204">
+        <f t="shared" si="93"/>
+        <v>1.89821</v>
+      </c>
+      <c r="G2204">
+        <v>295083592</v>
+      </c>
+      <c r="H2204" s="3">
+        <v>506000000000</v>
+      </c>
+      <c r="I2204">
+        <f t="shared" si="91"/>
+        <v>2202</v>
+      </c>
+      <c r="J2204">
+        <f>SUM($F$3:F2204)/I2204</f>
+        <v>1.1572298819255205</v>
+      </c>
+      <c r="K2204">
+        <f t="shared" si="92"/>
+        <v>1.7891298799999997</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2205" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B2205">
+        <v>1882.13</v>
+      </c>
+      <c r="C2205">
+        <v>1883.52</v>
+      </c>
+      <c r="D2205">
+        <v>1862.18</v>
+      </c>
+      <c r="E2205">
+        <v>1867.28</v>
+      </c>
+      <c r="F2205">
+        <f t="shared" si="93"/>
+        <v>1.8672800000000001</v>
+      </c>
+      <c r="G2205">
+        <v>258642475</v>
+      </c>
+      <c r="H2205" s="3">
+        <v>430977000000</v>
+      </c>
+      <c r="I2205">
+        <f t="shared" si="91"/>
+        <v>2203</v>
+      </c>
+      <c r="J2205">
+        <f>SUM($F$3:F2205)/I2205</f>
+        <v>1.1575521924648189</v>
+      </c>
+      <c r="K2205">
+        <f t="shared" si="92"/>
+        <v>1.7903097999999995</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2206" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B2206">
+        <v>1881.74</v>
+      </c>
+      <c r="C2206">
+        <v>1902.8</v>
+      </c>
+      <c r="D2206">
+        <v>1881.74</v>
+      </c>
+      <c r="E2206">
+        <v>1884.57</v>
+      </c>
+      <c r="F2206">
+        <f t="shared" si="93"/>
+        <v>1.8845699999999999</v>
+      </c>
+      <c r="G2206">
+        <v>256912301</v>
+      </c>
+      <c r="H2206" s="3">
+        <v>467180000000</v>
+      </c>
+      <c r="I2206">
+        <f t="shared" si="91"/>
+        <v>2204</v>
+      </c>
+      <c r="J2206">
+        <f>SUM($F$3:F2206)/I2206</f>
+        <v>1.1578820553539002</v>
+      </c>
+      <c r="K2206">
+        <f t="shared" si="92"/>
+        <v>1.7916386799999995</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2207" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B2207">
+        <v>1873.09</v>
+      </c>
+      <c r="C2207">
+        <v>1885.58</v>
+      </c>
+      <c r="D2207">
+        <v>1871.08</v>
+      </c>
+      <c r="E2207">
+        <v>1883.37</v>
+      </c>
+      <c r="F2207">
+        <f t="shared" si="93"/>
+        <v>1.88337</v>
+      </c>
+      <c r="G2207">
+        <v>239087370</v>
+      </c>
+      <c r="H2207" s="3">
+        <v>424087000000</v>
+      </c>
+      <c r="I2207">
+        <f t="shared" si="91"/>
+        <v>2205</v>
+      </c>
+      <c r="J2207">
+        <f>SUM($F$3:F2207)/I2207</f>
+        <v>1.1582110748299304</v>
+      </c>
+      <c r="K2207">
+        <f t="shared" si="92"/>
+        <v>1.7930003199999995</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2208" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2208">
+        <v>1900.19</v>
+      </c>
+      <c r="C2208">
+        <v>1905.56</v>
+      </c>
+      <c r="D2208">
+        <v>1884.53</v>
+      </c>
+      <c r="E2208">
+        <v>1905.56</v>
+      </c>
+      <c r="F2208">
+        <f t="shared" si="93"/>
+        <v>1.9055599999999999</v>
+      </c>
+      <c r="G2208">
+        <v>264003158</v>
+      </c>
+      <c r="H2208" s="3">
+        <v>475347000000</v>
+      </c>
+      <c r="I2208">
+        <f t="shared" si="91"/>
+        <v>2206</v>
+      </c>
+      <c r="J2208">
+        <f>SUM($F$3:F2208)/I2208</f>
+        <v>1.1585498549410682</v>
+      </c>
+      <c r="K2208">
+        <f t="shared" si="92"/>
+        <v>1.7944362399999996</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2209" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B2209">
+        <v>1914.45</v>
+      </c>
+      <c r="C2209">
+        <v>1918.01</v>
+      </c>
+      <c r="D2209">
+        <v>1894.57</v>
+      </c>
+      <c r="E2209">
+        <v>1898.69</v>
+      </c>
+      <c r="F2209">
+        <f t="shared" si="93"/>
+        <v>1.89869</v>
+      </c>
+      <c r="G2209">
+        <v>253613800</v>
+      </c>
+      <c r="H2209" s="3">
+        <v>476876000000</v>
+      </c>
+      <c r="I2209">
+        <f t="shared" si="91"/>
+        <v>2207</v>
+      </c>
+      <c r="J2209">
+        <f>SUM($F$3:F2209)/I2209</f>
+        <v>1.1588852152242848</v>
+      </c>
+      <c r="K2209">
+        <f t="shared" si="92"/>
+        <v>1.7958219199999994</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2210" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B2210">
+        <v>1903.37</v>
+      </c>
+      <c r="C2210">
+        <v>1935.45</v>
+      </c>
+      <c r="D2210">
+        <v>1900.99</v>
+      </c>
+      <c r="E2210">
+        <v>1933.99</v>
+      </c>
+      <c r="F2210">
+        <f t="shared" si="93"/>
+        <v>1.9339900000000001</v>
+      </c>
+      <c r="G2210">
+        <v>271049273</v>
+      </c>
+      <c r="H2210" s="3">
+        <v>499318000000</v>
+      </c>
+      <c r="I2210">
+        <f t="shared" si="91"/>
+        <v>2208</v>
+      </c>
+      <c r="J2210">
+        <f>SUM($F$3:F2210)/I2210</f>
+        <v>1.1592362590579695</v>
+      </c>
+      <c r="K2210">
+        <f t="shared" si="92"/>
+        <v>1.7974212399999994</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2211" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B2211">
+        <v>1928.44</v>
+      </c>
+      <c r="C2211">
+        <v>1937.81</v>
+      </c>
+      <c r="D2211">
+        <v>1917.11</v>
+      </c>
+      <c r="E2211">
+        <v>1933.45</v>
+      </c>
+      <c r="F2211">
+        <f t="shared" si="93"/>
+        <v>1.9334500000000001</v>
+      </c>
+      <c r="G2211">
+        <v>254590229</v>
+      </c>
+      <c r="H2211" s="3">
+        <v>471725000000</v>
+      </c>
+      <c r="I2211">
+        <f t="shared" si="91"/>
+        <v>2209</v>
+      </c>
+      <c r="J2211">
+        <f>SUM($F$3:F2211)/I2211</f>
+        <v>1.1595867406066076</v>
+      </c>
+      <c r="K2211">
+        <f t="shared" si="92"/>
+        <v>1.7998928799999994</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2212" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B2212">
+        <v>1932.65</v>
+      </c>
+      <c r="C2212">
+        <v>1951.8</v>
+      </c>
+      <c r="D2212">
+        <v>1930.5</v>
+      </c>
+      <c r="E2212">
+        <v>1951.04</v>
+      </c>
+      <c r="F2212">
+        <f t="shared" si="93"/>
+        <v>1.9510399999999999</v>
+      </c>
+      <c r="G2212">
+        <v>291161630</v>
+      </c>
+      <c r="H2212" s="3">
+        <v>542174000000</v>
+      </c>
+      <c r="I2212">
+        <f t="shared" si="91"/>
+        <v>2210</v>
+      </c>
+      <c r="J2212">
+        <f>SUM($F$3:F2212)/I2212</f>
+        <v>1.159944864253392</v>
+      </c>
+      <c r="K2212">
+        <f t="shared" si="92"/>
+        <v>1.8024115599999995</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2213" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B2213">
+        <v>1945.55</v>
+      </c>
+      <c r="C2213">
+        <v>1945.55</v>
+      </c>
+      <c r="D2213">
+        <v>1925.09</v>
+      </c>
+      <c r="E2213">
+        <v>1935.54</v>
+      </c>
+      <c r="F2213">
+        <f t="shared" si="93"/>
+        <v>1.93554</v>
+      </c>
+      <c r="G2213">
+        <v>257935461</v>
+      </c>
+      <c r="H2213" s="3">
+        <v>461892000000</v>
+      </c>
+      <c r="I2213">
+        <f t="shared" si="91"/>
+        <v>2211</v>
+      </c>
+      <c r="J2213">
+        <f>SUM($F$3:F2213)/I2213</f>
+        <v>1.1602956535504279</v>
+      </c>
+      <c r="K2213">
+        <f t="shared" si="92"/>
+        <v>1.8046677199999994</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2214" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B2214">
+        <v>1928.5</v>
+      </c>
+      <c r="C2214">
+        <v>1950.25</v>
+      </c>
+      <c r="D2214">
+        <v>1923.11</v>
+      </c>
+      <c r="E2214">
+        <v>1949.99</v>
+      </c>
+      <c r="F2214">
+        <f t="shared" si="93"/>
+        <v>1.9499900000000001</v>
+      </c>
+      <c r="G2214">
+        <v>266442608</v>
+      </c>
+      <c r="H2214" s="3">
+        <v>519751000000</v>
+      </c>
+      <c r="I2214">
+        <f t="shared" si="91"/>
+        <v>2212</v>
+      </c>
+      <c r="J2214">
+        <f>SUM($F$3:F2214)/I2214</f>
+        <v>1.1606526582278465</v>
+      </c>
+      <c r="K2214">
+        <f t="shared" si="92"/>
+        <v>1.8068120399999996</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2215" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B2215">
+        <v>1949.43</v>
+      </c>
+      <c r="C2215">
+        <v>1953.71</v>
+      </c>
+      <c r="D2215">
+        <v>1916.24</v>
+      </c>
+      <c r="E2215">
+        <v>1925.35</v>
+      </c>
+      <c r="F2215">
+        <f t="shared" si="93"/>
+        <v>1.9253499999999999</v>
+      </c>
+      <c r="G2215">
+        <v>294688267</v>
+      </c>
+      <c r="H2215" s="3">
+        <v>556805000000</v>
+      </c>
+      <c r="I2215">
+        <f t="shared" si="91"/>
+        <v>2213</v>
+      </c>
+      <c r="J2215">
+        <f>SUM($F$3:F2215)/I2215</f>
+        <v>1.1609982060551272</v>
+      </c>
+      <c r="K2215">
+        <f t="shared" si="92"/>
+        <v>1.8087894399999995</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2216" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B2216">
+        <v>1915.82</v>
+      </c>
+      <c r="C2216">
+        <v>1922.76</v>
+      </c>
+      <c r="D2216">
+        <v>1889.84</v>
+      </c>
+      <c r="E2216">
+        <v>1910.47</v>
+      </c>
+      <c r="F2216">
+        <f t="shared" si="93"/>
+        <v>1.9104700000000001</v>
+      </c>
+      <c r="G2216">
+        <v>282753316</v>
+      </c>
+      <c r="H2216" s="3">
+        <v>551610000000</v>
+      </c>
+      <c r="I2216">
+        <f t="shared" si="91"/>
+        <v>2214</v>
+      </c>
+      <c r="J2216">
+        <f>SUM($F$3:F2216)/I2216</f>
+        <v>1.161336720867207</v>
+      </c>
+      <c r="K2216">
+        <f t="shared" si="92"/>
+        <v>1.8106060799999997</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2217" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B2217">
+        <v>1905.85</v>
+      </c>
+      <c r="C2217">
+        <v>1926.07</v>
+      </c>
+      <c r="D2217">
+        <v>1887.13</v>
+      </c>
+      <c r="E2217">
+        <v>1924.78</v>
+      </c>
+      <c r="F2217">
+        <f t="shared" si="93"/>
+        <v>1.9247799999999999</v>
+      </c>
+      <c r="G2217">
+        <v>264608844</v>
+      </c>
+      <c r="H2217" s="3">
+        <v>523832000000</v>
+      </c>
+      <c r="I2217">
+        <f t="shared" si="91"/>
+        <v>2215</v>
+      </c>
+      <c r="J2217">
+        <f>SUM($F$3:F2217)/I2217</f>
+        <v>1.1616813905191856</v>
+      </c>
+      <c r="K2217">
+        <f t="shared" si="92"/>
+        <v>1.8124851599999996</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2218" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B2218">
+        <v>1915.66</v>
+      </c>
+      <c r="C2218">
+        <v>1917.78</v>
+      </c>
+      <c r="D2218">
+        <v>1886.26</v>
+      </c>
+      <c r="E2218">
+        <v>1893.68</v>
+      </c>
+      <c r="F2218">
+        <f t="shared" si="93"/>
+        <v>1.89368</v>
+      </c>
+      <c r="G2218">
+        <v>270054351</v>
+      </c>
+      <c r="H2218" s="3">
+        <v>515693000000</v>
+      </c>
+      <c r="I2218">
+        <f t="shared" si="91"/>
+        <v>2216</v>
+      </c>
+      <c r="J2218">
+        <f>SUM($F$3:F2218)/I2218</f>
+        <v>1.1620117148014422</v>
+      </c>
+      <c r="K2218">
+        <f t="shared" si="92"/>
+        <v>1.8143348799999997</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2219" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B2219">
+        <v>1884.43</v>
+      </c>
+      <c r="C2219">
+        <v>1921.44</v>
+      </c>
+      <c r="D2219">
+        <v>1884.43</v>
+      </c>
+      <c r="E2219">
+        <v>1915.28</v>
+      </c>
+      <c r="F2219">
+        <f t="shared" si="93"/>
+        <v>1.9152799999999999</v>
+      </c>
+      <c r="G2219">
+        <v>265023530</v>
+      </c>
+      <c r="H2219" s="3">
+        <v>499459000000</v>
+      </c>
+      <c r="I2219">
+        <f t="shared" si="91"/>
+        <v>2217</v>
+      </c>
+      <c r="J2219">
+        <f>SUM($F$3:F2219)/I2219</f>
+        <v>1.1623514839873685</v>
+      </c>
+      <c r="K2219">
+        <f t="shared" si="92"/>
+        <v>1.8162494399999995</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2220" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B2220">
+        <v>1914.49</v>
+      </c>
+      <c r="C2220">
+        <v>1929.22</v>
+      </c>
+      <c r="D2220">
+        <v>1913.83</v>
+      </c>
+      <c r="E2220">
+        <v>1926.67</v>
+      </c>
+      <c r="F2220">
+        <f t="shared" si="93"/>
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="G2220">
+        <v>277622194</v>
+      </c>
+      <c r="H2220" s="3">
+        <v>562335000000</v>
+      </c>
+      <c r="I2220">
+        <f t="shared" si="91"/>
+        <v>2218</v>
+      </c>
+      <c r="J2220">
+        <f>SUM($F$3:F2220)/I2220</f>
+        <v>1.1626960820559045</v>
+      </c>
+      <c r="K2220">
+        <f t="shared" si="92"/>
+        <v>1.8182105999999996</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2220"/>
+  <dimension ref="A1:K2238"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -81313,7 +81313,7 @@
         <v>1.119025302525011</v>
       </c>
       <c r="K2101">
-        <f t="shared" ref="K2101:K2163" si="90">SUM(F1852:F2101)/250</f>
+        <f t="shared" ref="K2101:K2165" si="90">SUM(F1852:F2101)/250</f>
         <v>1.6052981200000014</v>
       </c>
     </row>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2220" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2238" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -83809,7 +83809,7 @@
         <v>1.1428036569579276</v>
       </c>
       <c r="K2165">
-        <f t="shared" ref="K2165:K2220" si="92">SUM(F1916:F2165)/250</f>
+        <f t="shared" si="90"/>
         <v>1.7348080800000001</v>
       </c>
     </row>
@@ -83848,7 +83848,7 @@
         <v>1.1432135397412189</v>
       </c>
       <c r="K2166">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="K2166" si="92">SUM(F1917:F2166)/250</f>
         <v>1.7374636000000001</v>
       </c>
     </row>
@@ -83887,7 +83887,7 @@
         <v>1.1436169376443406</v>
       </c>
       <c r="K2167">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="K2167:K2230" si="93">SUM(F1918:F2167)/250</f>
         <v>1.7399060799999997</v>
       </c>
     </row>
@@ -83926,7 +83926,7 @@
         <v>1.1440173222529999</v>
       </c>
       <c r="K2168">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7423895599999997</v>
       </c>
     </row>
@@ -83965,7 +83965,7 @@
         <v>1.1444390078449458</v>
       </c>
       <c r="K2169">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7448529199999994</v>
       </c>
     </row>
@@ -84004,7 +84004,7 @@
         <v>1.1448667481549804</v>
       </c>
       <c r="K2170">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7471845999999995</v>
       </c>
     </row>
@@ -84043,7 +84043,7 @@
         <v>1.1452874550484085</v>
       </c>
       <c r="K2171">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7493396399999994</v>
       </c>
     </row>
@@ -84082,7 +84082,7 @@
         <v>1.1457104608294919</v>
       </c>
       <c r="K2172">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7512827599999998</v>
       </c>
     </row>
@@ -84121,7 +84121,7 @@
         <v>1.146127231690464</v>
       </c>
       <c r="K2173">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7531981199999997</v>
       </c>
     </row>
@@ -84160,7 +84160,7 @@
         <v>1.1465435497237557</v>
       </c>
       <c r="K2174">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7550117999999997</v>
       </c>
     </row>
@@ -84199,7 +84199,7 @@
         <v>1.1469647491946606</v>
       </c>
       <c r="K2175">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7569384399999994</v>
       </c>
     </row>
@@ -84238,7 +84238,7 @@
         <v>1.1473874609015629</v>
       </c>
       <c r="K2176">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7587543199999995</v>
       </c>
     </row>
@@ -84259,7 +84259,7 @@
         <v>2087.19</v>
       </c>
       <c r="F2177">
-        <f t="shared" ref="F2177:F2220" si="93">E2177/1000</f>
+        <f t="shared" ref="F2177:F2238" si="94">E2177/1000</f>
         <v>2.0871900000000001</v>
       </c>
       <c r="G2177">
@@ -84277,7 +84277,7 @@
         <v>1.1478195540229874</v>
       </c>
       <c r="K2177">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7605544399999997</v>
       </c>
     </row>
@@ -84298,7 +84298,7 @@
         <v>2033.9</v>
       </c>
       <c r="F2178">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.0339</v>
       </c>
       <c r="G2178">
@@ -84316,7 +84316,7 @@
         <v>1.1482267601102929</v>
       </c>
       <c r="K2178">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7623831999999995</v>
       </c>
     </row>
@@ -84337,7 +84337,7 @@
         <v>1948.74</v>
       </c>
       <c r="F2179">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9487399999999999</v>
       </c>
       <c r="G2179">
@@ -84355,7 +84355,7 @@
         <v>1.1485944740468523</v>
       </c>
       <c r="K2179">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7636799999999997</v>
       </c>
     </row>
@@ -84376,7 +84376,7 @@
         <v>1941.18</v>
       </c>
       <c r="F2180">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9411800000000001</v>
       </c>
       <c r="G2180">
@@ -84394,7 +84394,7 @@
         <v>1.1489583792470144</v>
       </c>
       <c r="K2180">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7648915199999997</v>
       </c>
     </row>
@@ -84415,7 +84415,7 @@
         <v>1970.63</v>
       </c>
       <c r="F2181">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9706300000000001</v>
       </c>
       <c r="G2181">
@@ -84433,7 +84433,7 @@
         <v>1.1493354658100032</v>
       </c>
       <c r="K2181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7660673199999997</v>
       </c>
     </row>
@@ -84454,7 +84454,7 @@
         <v>2001.07</v>
       </c>
       <c r="F2182">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.0010699999999999</v>
       </c>
       <c r="G2182">
@@ -84472,7 +84472,7 @@
         <v>1.1497261697247692</v>
       </c>
       <c r="K2182">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7673977999999999</v>
       </c>
     </row>
@@ -84493,7 +84493,7 @@
         <v>2002.92</v>
       </c>
       <c r="F2183">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.00292</v>
       </c>
       <c r="G2183">
@@ -84511,7 +84511,7 @@
         <v>1.1501173635946798</v>
       </c>
       <c r="K2183">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7687814000000002</v>
       </c>
     </row>
@@ -84532,7 +84532,7 @@
         <v>2037.7</v>
       </c>
       <c r="F2184">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.0377000000000001</v>
       </c>
       <c r="G2184">
@@ -84550,7 +84550,7 @@
         <v>1.1505241384051312</v>
       </c>
       <c r="K2184">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7702129599999998</v>
       </c>
     </row>
@@ -84571,7 +84571,7 @@
         <v>2028.27</v>
       </c>
       <c r="F2185">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.02827</v>
       </c>
       <c r="G2185">
@@ -84589,7 +84589,7 @@
         <v>1.1509262207970665</v>
       </c>
       <c r="K2185">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7716653600000003</v>
       </c>
     </row>
@@ -84610,7 +84610,7 @@
         <v>2005.8</v>
       </c>
       <c r="F2186">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.0057999999999998</v>
       </c>
       <c r="G2186">
@@ -84628,7 +84628,7 @@
         <v>1.1513176465201447</v>
       </c>
       <c r="K2186">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7733637200000001</v>
       </c>
     </row>
@@ -84649,7 +84649,7 @@
         <v>1975.8</v>
       </c>
       <c r="F2187">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9758</v>
       </c>
       <c r="G2187">
@@ -84667,7 +84667,7 @@
         <v>1.1516949839816917</v>
       </c>
       <c r="K2187">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.774915</v>
       </c>
     </row>
@@ -84688,7 +84688,7 @@
         <v>1984.4</v>
       </c>
       <c r="F2188">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9844000000000002</v>
       </c>
       <c r="G2188">
@@ -84706,7 +84706,7 @@
         <v>1.1520759103385161</v>
       </c>
       <c r="K2188">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7763529599999999</v>
       </c>
     </row>
@@ -84727,7 +84727,7 @@
         <v>1944.56</v>
       </c>
       <c r="F2189">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9445599999999998</v>
       </c>
       <c r="G2189">
@@ -84745,7 +84745,7 @@
         <v>1.1524382716049364</v>
       </c>
       <c r="K2189">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.77756808</v>
       </c>
     </row>
@@ -84766,7 +84766,7 @@
         <v>1978.71</v>
       </c>
       <c r="F2190">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.97871</v>
       </c>
       <c r="G2190">
@@ -84784,7 +84784,7 @@
         <v>1.1528159095063968</v>
       </c>
       <c r="K2190">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.77868016</v>
       </c>
     </row>
@@ -84805,7 +84805,7 @@
         <v>1936.5</v>
       </c>
       <c r="F2191">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9365000000000001</v>
       </c>
       <c r="G2191">
@@ -84823,7 +84823,7 @@
         <v>1.153173919597988</v>
       </c>
       <c r="K2191">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7796935599999999</v>
       </c>
     </row>
@@ -84844,7 +84844,7 @@
         <v>1878.89</v>
       </c>
       <c r="F2192">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8788900000000002</v>
       </c>
       <c r="G2192">
@@ -84862,7 +84862,7 @@
         <v>1.153505296803651</v>
       </c>
       <c r="K2192">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.780497</v>
       </c>
     </row>
@@ -84883,7 +84883,7 @@
         <v>1773.68</v>
       </c>
       <c r="F2193">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.7736800000000001</v>
       </c>
       <c r="G2193">
@@ -84901,7 +84901,7 @@
         <v>1.1537883523505228</v>
       </c>
       <c r="K2193">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.78087332</v>
       </c>
     </row>
@@ -84922,7 +84922,7 @@
         <v>1833.14</v>
       </c>
       <c r="F2194">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.83314</v>
       </c>
       <c r="G2194">
@@ -84940,7 +84940,7 @@
         <v>1.1540982755474434</v>
       </c>
       <c r="K2194">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7814226799999999</v>
       </c>
     </row>
@@ -84961,7 +84961,7 @@
         <v>1869.63</v>
       </c>
       <c r="F2195">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8696300000000001</v>
       </c>
       <c r="G2195">
@@ -84979,7 +84979,7 @@
         <v>1.1544245554035548</v>
       </c>
       <c r="K2195">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.78225568</v>
       </c>
     </row>
@@ -85000,7 +85000,7 @@
         <v>1831.78</v>
       </c>
       <c r="F2196">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.83178</v>
       </c>
       <c r="G2196">
@@ -85018,7 +85018,7 @@
         <v>1.1547332862351849</v>
       </c>
       <c r="K2196">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7828171599999998</v>
       </c>
     </row>
@@ -85039,7 +85039,7 @@
         <v>1853.94</v>
       </c>
       <c r="F2197">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8539400000000001</v>
       </c>
       <c r="G2197">
@@ -85057,7 +85057,7 @@
         <v>1.1550518314350777</v>
       </c>
       <c r="K2197">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.78344828</v>
       </c>
     </row>
@@ -85078,7 +85078,7 @@
         <v>1856.99</v>
       </c>
       <c r="F2198">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8569899999999999</v>
       </c>
       <c r="G2198">
@@ -85096,7 +85096,7 @@
         <v>1.1553714754098343</v>
       </c>
       <c r="K2198">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7840578</v>
       </c>
     </row>
@@ -85117,7 +85117,7 @@
         <v>1834.35</v>
       </c>
       <c r="F2199">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8343499999999999</v>
       </c>
       <c r="G2199">
@@ -85135,7 +85135,7 @@
         <v>1.1556805234410541</v>
       </c>
       <c r="K2199">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7846445999999998</v>
       </c>
     </row>
@@ -85156,7 +85156,7 @@
         <v>1866.82</v>
       </c>
       <c r="F2200">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8668199999999999</v>
       </c>
       <c r="G2200">
@@ -85174,7 +85174,7 @@
         <v>1.1560040627843478</v>
       </c>
       <c r="K2200">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7854003199999999</v>
       </c>
     </row>
@@ -85195,7 +85195,7 @@
         <v>1826.24</v>
       </c>
       <c r="F2201">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8262400000000001</v>
       </c>
       <c r="G2201">
@@ -85213,7 +85213,7 @@
         <v>1.1563088540245547</v>
       </c>
       <c r="K2201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7861601199999999</v>
       </c>
     </row>
@@ -85234,7 +85234,7 @@
         <v>1790.35</v>
       </c>
       <c r="F2202">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.7903499999999999</v>
       </c>
       <c r="G2202">
@@ -85252,7 +85252,7 @@
         <v>1.1565970545454529</v>
       </c>
       <c r="K2202">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7869274399999997</v>
       </c>
     </row>
@@ -85273,7 +85273,7 @@
         <v>1808.47</v>
       </c>
       <c r="F2203">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.80847</v>
       </c>
       <c r="G2203">
@@ -85291,7 +85291,7 @@
         <v>1.1568932258064499</v>
       </c>
       <c r="K2203">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7878681999999997</v>
       </c>
     </row>
@@ -85312,7 +85312,7 @@
         <v>1898.21</v>
       </c>
       <c r="F2204">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.89821</v>
       </c>
       <c r="G2204">
@@ -85330,7 +85330,7 @@
         <v>1.1572298819255205</v>
       </c>
       <c r="K2204">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7891298799999997</v>
       </c>
     </row>
@@ -85351,7 +85351,7 @@
         <v>1867.28</v>
       </c>
       <c r="F2205">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8672800000000001</v>
       </c>
       <c r="G2205">
@@ -85369,7 +85369,7 @@
         <v>1.1575521924648189</v>
       </c>
       <c r="K2205">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7903097999999995</v>
       </c>
     </row>
@@ -85390,7 +85390,7 @@
         <v>1884.57</v>
       </c>
       <c r="F2206">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.8845699999999999</v>
       </c>
       <c r="G2206">
@@ -85408,7 +85408,7 @@
         <v>1.1578820553539002</v>
       </c>
       <c r="K2206">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7916386799999995</v>
       </c>
     </row>
@@ -85429,7 +85429,7 @@
         <v>1883.37</v>
       </c>
       <c r="F2207">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.88337</v>
       </c>
       <c r="G2207">
@@ -85447,7 +85447,7 @@
         <v>1.1582110748299304</v>
       </c>
       <c r="K2207">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7930003199999995</v>
       </c>
     </row>
@@ -85468,7 +85468,7 @@
         <v>1905.56</v>
       </c>
       <c r="F2208">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9055599999999999</v>
       </c>
       <c r="G2208">
@@ -85486,7 +85486,7 @@
         <v>1.1585498549410682</v>
       </c>
       <c r="K2208">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7944362399999996</v>
       </c>
     </row>
@@ -85507,7 +85507,7 @@
         <v>1898.69</v>
       </c>
       <c r="F2209">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.89869</v>
       </c>
       <c r="G2209">
@@ -85525,7 +85525,7 @@
         <v>1.1588852152242848</v>
       </c>
       <c r="K2209">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7958219199999994</v>
       </c>
     </row>
@@ -85546,7 +85546,7 @@
         <v>1933.99</v>
       </c>
       <c r="F2210">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9339900000000001</v>
       </c>
       <c r="G2210">
@@ -85564,7 +85564,7 @@
         <v>1.1592362590579695</v>
       </c>
       <c r="K2210">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7974212399999994</v>
       </c>
     </row>
@@ -85585,7 +85585,7 @@
         <v>1933.45</v>
       </c>
       <c r="F2211">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9334500000000001</v>
       </c>
       <c r="G2211">
@@ -85603,7 +85603,7 @@
         <v>1.1595867406066076</v>
       </c>
       <c r="K2211">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.7998928799999994</v>
       </c>
     </row>
@@ -85624,7 +85624,7 @@
         <v>1951.04</v>
       </c>
       <c r="F2212">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9510399999999999</v>
       </c>
       <c r="G2212">
@@ -85642,7 +85642,7 @@
         <v>1.159944864253392</v>
       </c>
       <c r="K2212">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8024115599999995</v>
       </c>
     </row>
@@ -85663,7 +85663,7 @@
         <v>1935.54</v>
       </c>
       <c r="F2213">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.93554</v>
       </c>
       <c r="G2213">
@@ -85681,7 +85681,7 @@
         <v>1.1602956535504279</v>
       </c>
       <c r="K2213">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8046677199999994</v>
       </c>
     </row>
@@ -85702,7 +85702,7 @@
         <v>1949.99</v>
       </c>
       <c r="F2214">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9499900000000001</v>
       </c>
       <c r="G2214">
@@ -85720,7 +85720,7 @@
         <v>1.1606526582278465</v>
       </c>
       <c r="K2214">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8068120399999996</v>
       </c>
     </row>
@@ -85741,7 +85741,7 @@
         <v>1925.35</v>
       </c>
       <c r="F2215">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9253499999999999</v>
       </c>
       <c r="G2215">
@@ -85759,7 +85759,7 @@
         <v>1.1609982060551272</v>
       </c>
       <c r="K2215">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8087894399999995</v>
       </c>
     </row>
@@ -85780,7 +85780,7 @@
         <v>1910.47</v>
       </c>
       <c r="F2216">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9104700000000001</v>
       </c>
       <c r="G2216">
@@ -85798,7 +85798,7 @@
         <v>1.161336720867207</v>
       </c>
       <c r="K2216">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8106060799999997</v>
       </c>
     </row>
@@ -85819,7 +85819,7 @@
         <v>1924.78</v>
       </c>
       <c r="F2217">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9247799999999999</v>
       </c>
       <c r="G2217">
@@ -85837,7 +85837,7 @@
         <v>1.1616813905191856</v>
       </c>
       <c r="K2217">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8124851599999996</v>
       </c>
     </row>
@@ -85858,7 +85858,7 @@
         <v>1893.68</v>
       </c>
       <c r="F2218">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.89368</v>
       </c>
       <c r="G2218">
@@ -85876,7 +85876,7 @@
         <v>1.1620117148014422</v>
       </c>
       <c r="K2218">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8143348799999997</v>
       </c>
     </row>
@@ -85897,7 +85897,7 @@
         <v>1915.28</v>
       </c>
       <c r="F2219">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9152799999999999</v>
       </c>
       <c r="G2219">
@@ -85915,7 +85915,7 @@
         <v>1.1623514839873685</v>
       </c>
       <c r="K2219">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8162494399999995</v>
       </c>
     </row>
@@ -85936,7 +85936,7 @@
         <v>1926.67</v>
       </c>
       <c r="F2220">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.9266700000000001</v>
       </c>
       <c r="G2220">
@@ -85954,8 +85954,710 @@
         <v>1.1626960820559045</v>
       </c>
       <c r="K2220">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1.8182105999999996</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2221" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B2221">
+        <v>1940.7</v>
+      </c>
+      <c r="C2221">
+        <v>1971.53</v>
+      </c>
+      <c r="D2221">
+        <v>1940.7</v>
+      </c>
+      <c r="E2221">
+        <v>1962.93</v>
+      </c>
+      <c r="F2221">
+        <f t="shared" si="94"/>
+        <v>1.9629300000000001</v>
+      </c>
+      <c r="G2221">
+        <v>315924354</v>
+      </c>
+      <c r="H2221" s="3">
+        <v>698462000000</v>
+      </c>
+      <c r="I2221">
+        <f t="shared" si="91"/>
+        <v>2219</v>
+      </c>
+      <c r="J2221">
+        <f>SUM($F$3:F2221)/I2221</f>
+        <v>1.1630567102298315</v>
+      </c>
+      <c r="K2221">
+        <f t="shared" si="93"/>
+        <v>1.8201809199999999</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2222" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B2222">
+        <v>1967.97</v>
+      </c>
+      <c r="C2222">
+        <v>1993.82</v>
+      </c>
+      <c r="D2222">
+        <v>1966.6</v>
+      </c>
+      <c r="E2222">
+        <v>1993.62</v>
+      </c>
+      <c r="F2222">
+        <f t="shared" si="94"/>
+        <v>1.9936199999999999</v>
+      </c>
+      <c r="G2222">
+        <v>323106760</v>
+      </c>
+      <c r="H2222" s="3">
+        <v>659418000000</v>
+      </c>
+      <c r="I2222">
+        <f t="shared" si="91"/>
+        <v>2220</v>
+      </c>
+      <c r="J2222">
+        <f>SUM($F$3:F2222)/I2222</f>
+        <v>1.1634308378378362</v>
+      </c>
+      <c r="K2222">
+        <f t="shared" si="93"/>
+        <v>1.8222926399999995</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2223" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B2223">
+        <v>1991.5</v>
+      </c>
+      <c r="C2223">
+        <v>2015.11</v>
+      </c>
+      <c r="D2223">
+        <v>1987.95</v>
+      </c>
+      <c r="E2223">
+        <v>2012.35</v>
+      </c>
+      <c r="F2223">
+        <f t="shared" si="94"/>
+        <v>2.0123500000000001</v>
+      </c>
+      <c r="G2223">
+        <v>342574411</v>
+      </c>
+      <c r="H2223" s="3">
+        <v>669348000000</v>
+      </c>
+      <c r="I2223">
+        <f t="shared" si="91"/>
+        <v>2221</v>
+      </c>
+      <c r="J2223">
+        <f>SUM($F$3:F2223)/I2223</f>
+        <v>1.1638130616839246</v>
+      </c>
+      <c r="K2223">
+        <f t="shared" si="93"/>
+        <v>1.8244208399999997</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2224" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B2224">
+        <v>2023.78</v>
+      </c>
+      <c r="C2224">
+        <v>2029.48</v>
+      </c>
+      <c r="D2224">
+        <v>2010.61</v>
+      </c>
+      <c r="E2224">
+        <v>2029.1</v>
+      </c>
+      <c r="F2224">
+        <f t="shared" si="94"/>
+        <v>2.0291000000000001</v>
+      </c>
+      <c r="G2224">
+        <v>370322548</v>
+      </c>
+      <c r="H2224" s="3">
+        <v>768399000000</v>
+      </c>
+      <c r="I2224">
+        <f t="shared" si="91"/>
+        <v>2222</v>
+      </c>
+      <c r="J2224">
+        <f>SUM($F$3:F2224)/I2224</f>
+        <v>1.1642024797479733</v>
+      </c>
+      <c r="K2224">
+        <f t="shared" si="93"/>
+        <v>1.82673084</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2225" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B2225">
+        <v>2027.18</v>
+      </c>
+      <c r="C2225">
+        <v>2027.18</v>
+      </c>
+      <c r="D2225">
+        <v>1996.18</v>
+      </c>
+      <c r="E2225">
+        <v>2003.61</v>
+      </c>
+      <c r="F2225">
+        <f t="shared" si="94"/>
+        <v>2.0036100000000001</v>
+      </c>
+      <c r="G2225">
+        <v>322335681</v>
+      </c>
+      <c r="H2225" s="3">
+        <v>654858000000</v>
+      </c>
+      <c r="I2225">
+        <f t="shared" si="91"/>
+        <v>2223</v>
+      </c>
+      <c r="J2225">
+        <f>SUM($F$3:F2225)/I2225</f>
+        <v>1.1645800809716584</v>
+      </c>
+      <c r="K2225">
+        <f t="shared" si="93"/>
+        <v>1.8289167200000001</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2226" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B2226">
+        <v>1997.54</v>
+      </c>
+      <c r="C2226">
+        <v>2026.48</v>
+      </c>
+      <c r="D2226">
+        <v>1992.88</v>
+      </c>
+      <c r="E2226">
+        <v>2026.35</v>
+      </c>
+      <c r="F2226">
+        <f t="shared" si="94"/>
+        <v>2.0263499999999999</v>
+      </c>
+      <c r="G2226">
+        <v>327272660</v>
+      </c>
+      <c r="H2226" s="3">
+        <v>685273000000</v>
+      </c>
+      <c r="I2226">
+        <f t="shared" si="91"/>
+        <v>2224</v>
+      </c>
+      <c r="J2226">
+        <f>SUM($F$3:F2226)/I2226</f>
+        <v>1.1649675674460418</v>
+      </c>
+      <c r="K2226">
+        <f t="shared" si="93"/>
+        <v>1.8312603999999999</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2227" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B2227">
+        <v>2034.46</v>
+      </c>
+      <c r="C2227">
+        <v>2036</v>
+      </c>
+      <c r="D2227">
+        <v>1976.7</v>
+      </c>
+      <c r="E2227">
+        <v>1976.7</v>
+      </c>
+      <c r="F2227">
+        <f t="shared" si="94"/>
+        <v>1.9767000000000001</v>
+      </c>
+      <c r="G2227">
+        <v>342265881</v>
+      </c>
+      <c r="H2227" s="3">
+        <v>705680000000</v>
+      </c>
+      <c r="I2227">
+        <f t="shared" si="91"/>
+        <v>2225</v>
+      </c>
+      <c r="J2227">
+        <f>SUM($F$3:F2227)/I2227</f>
+        <v>1.1653323910112345</v>
+      </c>
+      <c r="K2227">
+        <f t="shared" si="93"/>
+        <v>1.8333593999999998</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2228" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B2228">
+        <v>1977.76</v>
+      </c>
+      <c r="C2228">
+        <v>1999.42</v>
+      </c>
+      <c r="D2228">
+        <v>1955.23</v>
+      </c>
+      <c r="E2228">
+        <v>1968.05</v>
+      </c>
+      <c r="F2228">
+        <f t="shared" si="94"/>
+        <v>1.9680499999999999</v>
+      </c>
+      <c r="G2228">
+        <v>318769219</v>
+      </c>
+      <c r="H2228" s="3">
+        <v>679981000000</v>
+      </c>
+      <c r="I2228">
+        <f t="shared" si="91"/>
+        <v>2226</v>
+      </c>
+      <c r="J2228">
+        <f>SUM($F$3:F2228)/I2228</f>
+        <v>1.1656930008984712</v>
+      </c>
+      <c r="K2228">
+        <f t="shared" si="93"/>
+        <v>1.8353074799999998</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2229" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B2229">
+        <v>1964.41</v>
+      </c>
+      <c r="C2229">
+        <v>1986.59</v>
+      </c>
+      <c r="D2229">
+        <v>1955.58</v>
+      </c>
+      <c r="E2229">
+        <v>1980.19</v>
+      </c>
+      <c r="F2229">
+        <f t="shared" si="94"/>
+        <v>1.9801900000000001</v>
+      </c>
+      <c r="G2229">
+        <v>289963812</v>
+      </c>
+      <c r="H2229" s="3">
+        <v>589731000000</v>
+      </c>
+      <c r="I2229">
+        <f t="shared" si="91"/>
+        <v>2227</v>
+      </c>
+      <c r="J2229">
+        <f>SUM($F$3:F2229)/I2229</f>
+        <v>1.1660587382128411</v>
+      </c>
+      <c r="K2229">
+        <f t="shared" si="93"/>
+        <v>1.8371117999999995</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2230" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B2230">
+        <v>1977.35</v>
+      </c>
+      <c r="C2230">
+        <v>2012.79</v>
+      </c>
+      <c r="D2230">
+        <v>1976.24</v>
+      </c>
+      <c r="E2230">
+        <v>2012.78</v>
+      </c>
+      <c r="F2230">
+        <f t="shared" si="94"/>
+        <v>2.0127799999999998</v>
+      </c>
+      <c r="G2230">
+        <v>307703474</v>
+      </c>
+      <c r="H2230" s="3">
+        <v>630121000000</v>
+      </c>
+      <c r="I2230">
+        <f t="shared" si="91"/>
+        <v>2228</v>
+      </c>
+      <c r="J2230">
+        <f>SUM($F$3:F2230)/I2230</f>
+        <v>1.1664387746858156</v>
+      </c>
+      <c r="K2230">
+        <f t="shared" si="93"/>
+        <v>1.8390266799999997</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2231" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B2231">
+        <v>2004.15</v>
+      </c>
+      <c r="C2231">
+        <v>2005.55</v>
+      </c>
+      <c r="D2231">
+        <v>1977.05</v>
+      </c>
+      <c r="E2231">
+        <v>1985.87</v>
+      </c>
+      <c r="F2231">
+        <f t="shared" si="94"/>
+        <v>1.9858699999999998</v>
+      </c>
+      <c r="G2231">
+        <v>295764450</v>
+      </c>
+      <c r="H2231" s="3">
+        <v>612206000000</v>
+      </c>
+      <c r="I2231">
+        <f t="shared" si="91"/>
+        <v>2229</v>
+      </c>
+      <c r="J2231">
+        <f>SUM($F$3:F2231)/I2231</f>
+        <v>1.1668063974876615</v>
+      </c>
+      <c r="K2231">
+        <f t="shared" ref="K2231:K2238" si="95">SUM(F1982:F2231)/250</f>
+        <v>1.8407580399999994</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2232" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B2232">
+        <v>1991.32</v>
+      </c>
+      <c r="C2232">
+        <v>2006.06</v>
+      </c>
+      <c r="D2232">
+        <v>1920.26</v>
+      </c>
+      <c r="E2232">
+        <v>1922.6</v>
+      </c>
+      <c r="F2232">
+        <f t="shared" si="94"/>
+        <v>1.9225999999999999</v>
+      </c>
+      <c r="G2232">
+        <v>341470896</v>
+      </c>
+      <c r="H2232" s="3">
+        <v>726917000000</v>
+      </c>
+      <c r="I2232">
+        <f t="shared" si="91"/>
+        <v>2230</v>
+      </c>
+      <c r="J2232">
+        <f>SUM($F$3:F2232)/I2232</f>
+        <v>1.1671453183856488</v>
+      </c>
+      <c r="K2232">
+        <f t="shared" si="95"/>
+        <v>1.8423440399999997</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2233" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B2233">
+        <v>1935.14</v>
+      </c>
+      <c r="C2233">
+        <v>1956.8</v>
+      </c>
+      <c r="D2233">
+        <v>1915.54</v>
+      </c>
+      <c r="E2233">
+        <v>1949.23</v>
+      </c>
+      <c r="F2233">
+        <f t="shared" si="94"/>
+        <v>1.94923</v>
+      </c>
+      <c r="G2233">
+        <v>311508538</v>
+      </c>
+      <c r="H2233" s="3">
+        <v>574086000000</v>
+      </c>
+      <c r="I2233">
+        <f t="shared" si="91"/>
+        <v>2231</v>
+      </c>
+      <c r="J2233">
+        <f>SUM($F$3:F2233)/I2233</f>
+        <v>1.1674958718063637</v>
+      </c>
+      <c r="K2233">
+        <f t="shared" si="95"/>
+        <v>1.8439231599999999</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2234" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B2234">
+        <v>1957.46</v>
+      </c>
+      <c r="C2234">
+        <v>1968.07</v>
+      </c>
+      <c r="D2234">
+        <v>1932.34</v>
+      </c>
+      <c r="E2234">
+        <v>1951.33</v>
+      </c>
+      <c r="F2234">
+        <f t="shared" si="94"/>
+        <v>1.95133</v>
+      </c>
+      <c r="G2234">
+        <v>311623274</v>
+      </c>
+      <c r="H2234" s="3">
+        <v>638166000000</v>
+      </c>
+      <c r="I2234">
+        <f t="shared" si="91"/>
+        <v>2232</v>
+      </c>
+      <c r="J2234">
+        <f>SUM($F$3:F2234)/I2234</f>
+        <v>1.1678470519713249</v>
+      </c>
+      <c r="K2234">
+        <f t="shared" si="95"/>
+        <v>1.8455429599999997</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2235" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B2235">
+        <v>1942.03</v>
+      </c>
+      <c r="C2235">
+        <v>1942.03</v>
+      </c>
+      <c r="D2235">
+        <v>1891.18</v>
+      </c>
+      <c r="E2235">
+        <v>1918.33</v>
+      </c>
+      <c r="F2235">
+        <f t="shared" si="94"/>
+        <v>1.9183299999999999</v>
+      </c>
+      <c r="G2235">
+        <v>334261049</v>
+      </c>
+      <c r="H2235" s="3">
+        <v>642644000000</v>
+      </c>
+      <c r="I2235">
+        <f t="shared" si="91"/>
+        <v>2233</v>
+      </c>
+      <c r="J2235">
+        <f>SUM($F$3:F2235)/I2235</f>
+        <v>1.1681831392745172</v>
+      </c>
+      <c r="K2235">
+        <f t="shared" si="95"/>
+        <v>1.8470127199999995</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2236" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B2236">
+        <v>1915.98</v>
+      </c>
+      <c r="C2236">
+        <v>1923.69</v>
+      </c>
+      <c r="D2236">
+        <v>1864.72</v>
+      </c>
+      <c r="E2236">
+        <v>1873.58</v>
+      </c>
+      <c r="F2236">
+        <f t="shared" si="94"/>
+        <v>1.87358</v>
+      </c>
+      <c r="G2236">
+        <v>326128149</v>
+      </c>
+      <c r="H2236" s="3">
+        <v>648544000000</v>
+      </c>
+      <c r="I2236">
+        <f t="shared" si="91"/>
+        <v>2234</v>
+      </c>
+      <c r="J2236">
+        <f>SUM($F$3:F2236)/I2236</f>
+        <v>1.1684988943598913</v>
+      </c>
+      <c r="K2236">
+        <f t="shared" si="95"/>
+        <v>1.8484217199999997</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2237" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B2237">
+        <v>1871.21</v>
+      </c>
+      <c r="C2237">
+        <v>1893.51</v>
+      </c>
+      <c r="D2237">
+        <v>1845.16</v>
+      </c>
+      <c r="E2237">
+        <v>1884.24</v>
+      </c>
+      <c r="F2237">
+        <f t="shared" si="94"/>
+        <v>1.8842399999999999</v>
+      </c>
+      <c r="G2237">
+        <v>296261317</v>
+      </c>
+      <c r="H2237" s="3">
+        <v>575371000000</v>
+      </c>
+      <c r="I2237">
+        <f t="shared" si="91"/>
+        <v>2235</v>
+      </c>
+      <c r="J2237">
+        <f>SUM($F$3:F2237)/I2237</f>
+        <v>1.1688191364653229</v>
+      </c>
+      <c r="K2237">
+        <f t="shared" si="95"/>
+        <v>1.84984924</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2238" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B2238">
+        <v>1890.66</v>
+      </c>
+      <c r="C2238">
+        <v>1897.34</v>
+      </c>
+      <c r="D2238">
+        <v>1825.69</v>
+      </c>
+      <c r="E2238">
+        <v>1833.13</v>
+      </c>
+      <c r="F2238">
+        <f t="shared" si="94"/>
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="G2238">
+        <v>324754485</v>
+      </c>
+      <c r="H2238" s="3">
+        <v>637005000000</v>
+      </c>
+      <c r="I2238">
+        <f t="shared" si="91"/>
+        <v>2236</v>
+      </c>
+      <c r="J2238">
+        <f>SUM($F$3:F2238)/I2238</f>
+        <v>1.1691162343470469</v>
+      </c>
+      <c r="K2238">
+        <f t="shared" si="95"/>
+        <v>1.8510212799999999</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2238"/>
+  <dimension ref="A1:K2259"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2238" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2259" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -84259,7 +84259,7 @@
         <v>2087.19</v>
       </c>
       <c r="F2177">
-        <f t="shared" ref="F2177:F2238" si="94">E2177/1000</f>
+        <f t="shared" ref="F2177:F2259" si="94">E2177/1000</f>
         <v>2.0871900000000001</v>
       </c>
       <c r="G2177">
@@ -86383,7 +86383,7 @@
         <v>1.1668063974876615</v>
       </c>
       <c r="K2231">
-        <f t="shared" ref="K2231:K2238" si="95">SUM(F1982:F2231)/250</f>
+        <f t="shared" ref="K2231:K2259" si="95">SUM(F1982:F2231)/250</f>
         <v>1.8407580399999994</v>
       </c>
     </row>
@@ -86658,6 +86658,825 @@
       <c r="K2238">
         <f t="shared" si="95"/>
         <v>1.8510212799999999</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2239" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B2239">
+        <v>1831.59</v>
+      </c>
+      <c r="C2239">
+        <v>1884.67</v>
+      </c>
+      <c r="D2239">
+        <v>1829.82</v>
+      </c>
+      <c r="E2239">
+        <v>1865.39</v>
+      </c>
+      <c r="F2239">
+        <f t="shared" si="94"/>
+        <v>1.8653900000000001</v>
+      </c>
+      <c r="G2239">
+        <v>299755574</v>
+      </c>
+      <c r="H2239" s="3">
+        <v>579535000000</v>
+      </c>
+      <c r="I2239">
+        <f t="shared" si="91"/>
+        <v>2237</v>
+      </c>
+      <c r="J2239">
+        <f>SUM($F$3:F2239)/I2239</f>
+        <v>1.1694274877067488</v>
+      </c>
+      <c r="K2239">
+        <f t="shared" si="95"/>
+        <v>1.8522509199999997</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2240" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B2240">
+        <v>1867.35</v>
+      </c>
+      <c r="C2240">
+        <v>1868.82</v>
+      </c>
+      <c r="D2240">
+        <v>1819.48</v>
+      </c>
+      <c r="E2240">
+        <v>1845.18</v>
+      </c>
+      <c r="F2240">
+        <f t="shared" si="94"/>
+        <v>1.84518</v>
+      </c>
+      <c r="G2240">
+        <v>280541517</v>
+      </c>
+      <c r="H2240" s="3">
+        <v>540941000000</v>
+      </c>
+      <c r="I2240">
+        <f t="shared" si="91"/>
+        <v>2238</v>
+      </c>
+      <c r="J2240">
+        <f>SUM($F$3:F2240)/I2240</f>
+        <v>1.1697294325290422</v>
+      </c>
+      <c r="K2240">
+        <f t="shared" si="95"/>
+        <v>1.8534557600000001</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2241" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B2241">
+        <v>1840.57</v>
+      </c>
+      <c r="C2241">
+        <v>1853.41</v>
+      </c>
+      <c r="D2241">
+        <v>1817.4</v>
+      </c>
+      <c r="E2241">
+        <v>1831.55</v>
+      </c>
+      <c r="F2241">
+        <f t="shared" si="94"/>
+        <v>1.83155</v>
+      </c>
+      <c r="G2241">
+        <v>294534496</v>
+      </c>
+      <c r="H2241" s="3">
+        <v>604074000000</v>
+      </c>
+      <c r="I2241">
+        <f t="shared" si="91"/>
+        <v>2239</v>
+      </c>
+      <c r="J2241">
+        <f>SUM($F$3:F2241)/I2241</f>
+        <v>1.1700250200982565</v>
+      </c>
+      <c r="K2241">
+        <f t="shared" si="95"/>
+        <v>1.85466076</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2242" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B2242">
+        <v>1818.16</v>
+      </c>
+      <c r="C2242">
+        <v>1828.61</v>
+      </c>
+      <c r="D2242">
+        <v>1792.82</v>
+      </c>
+      <c r="E2242">
+        <v>1804.38</v>
+      </c>
+      <c r="F2242">
+        <f t="shared" si="94"/>
+        <v>1.8043800000000001</v>
+      </c>
+      <c r="G2242">
+        <v>264147613</v>
+      </c>
+      <c r="H2242" s="3">
+        <v>502064000000</v>
+      </c>
+      <c r="I2242">
+        <f t="shared" si="91"/>
+        <v>2240</v>
+      </c>
+      <c r="J2242">
+        <f>SUM($F$3:F2242)/I2242</f>
+        <v>1.1703082142857126</v>
+      </c>
+      <c r="K2242">
+        <f t="shared" si="95"/>
+        <v>1.8558563199999998</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2243" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B2243">
+        <v>1804.94</v>
+      </c>
+      <c r="C2243">
+        <v>1842.39</v>
+      </c>
+      <c r="D2243">
+        <v>1787.54</v>
+      </c>
+      <c r="E2243">
+        <v>1816.9</v>
+      </c>
+      <c r="F2243">
+        <f t="shared" si="94"/>
+        <v>1.8169000000000002</v>
+      </c>
+      <c r="G2243">
+        <v>321255471</v>
+      </c>
+      <c r="H2243" s="3">
+        <v>588903000000</v>
+      </c>
+      <c r="I2243">
+        <f t="shared" si="91"/>
+        <v>2241</v>
+      </c>
+      <c r="J2243">
+        <f>SUM($F$3:F2243)/I2243</f>
+        <v>1.1705967425256565</v>
+      </c>
+      <c r="K2243">
+        <f t="shared" si="95"/>
+        <v>1.8570048399999999</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2244" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B2244">
+        <v>1771.73</v>
+      </c>
+      <c r="C2244">
+        <v>1815.28</v>
+      </c>
+      <c r="D2244">
+        <v>1751.83</v>
+      </c>
+      <c r="E2244">
+        <v>1775.17</v>
+      </c>
+      <c r="F2244">
+        <f t="shared" si="94"/>
+        <v>1.7751700000000001</v>
+      </c>
+      <c r="G2244">
+        <v>309547094</v>
+      </c>
+      <c r="H2244" s="3">
+        <v>547997000000</v>
+      </c>
+      <c r="I2244">
+        <f t="shared" si="91"/>
+        <v>2242</v>
+      </c>
+      <c r="J2244">
+        <f>SUM($F$3:F2244)/I2244</f>
+        <v>1.1708664005352347</v>
+      </c>
+      <c r="K2244">
+        <f t="shared" si="95"/>
+        <v>1.85800312</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2245" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B2245">
+        <v>1790.25</v>
+      </c>
+      <c r="C2245">
+        <v>1799.14</v>
+      </c>
+      <c r="D2245">
+        <v>1769.39</v>
+      </c>
+      <c r="E2245">
+        <v>1799.14</v>
+      </c>
+      <c r="F2245">
+        <f t="shared" si="94"/>
+        <v>1.7991400000000002</v>
+      </c>
+      <c r="G2245">
+        <v>274427960</v>
+      </c>
+      <c r="H2245" s="3">
+        <v>498178000000</v>
+      </c>
+      <c r="I2245">
+        <f t="shared" si="91"/>
+        <v>2243</v>
+      </c>
+      <c r="J2245">
+        <f>SUM($F$3:F2245)/I2245</f>
+        <v>1.1711465046812288</v>
+      </c>
+      <c r="K2245">
+        <f t="shared" si="95"/>
+        <v>1.85912224</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2246" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B2246">
+        <v>1785.61</v>
+      </c>
+      <c r="C2246">
+        <v>1799.34</v>
+      </c>
+      <c r="D2246">
+        <v>1752.27</v>
+      </c>
+      <c r="E2246">
+        <v>1771.53</v>
+      </c>
+      <c r="F2246">
+        <f t="shared" si="94"/>
+        <v>1.77153</v>
+      </c>
+      <c r="G2246">
+        <v>277084778</v>
+      </c>
+      <c r="H2246" s="3">
+        <v>505063000000</v>
+      </c>
+      <c r="I2246">
+        <f t="shared" si="91"/>
+        <v>2244</v>
+      </c>
+      <c r="J2246">
+        <f>SUM($F$3:F2246)/I2246</f>
+        <v>1.1714140552584653</v>
+      </c>
+      <c r="K2246">
+        <f t="shared" si="95"/>
+        <v>1.8599544399999999</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2247" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B2247">
+        <v>1756.28</v>
+      </c>
+      <c r="C2247">
+        <v>1759.24</v>
+      </c>
+      <c r="D2247">
+        <v>1713.68</v>
+      </c>
+      <c r="E2247">
+        <v>1729.8</v>
+      </c>
+      <c r="F2247">
+        <f t="shared" si="94"/>
+        <v>1.7298</v>
+      </c>
+      <c r="G2247">
+        <v>258886647</v>
+      </c>
+      <c r="H2247" s="3">
+        <v>453238000000</v>
+      </c>
+      <c r="I2247">
+        <f t="shared" si="91"/>
+        <v>2245</v>
+      </c>
+      <c r="J2247">
+        <f>SUM($F$3:F2247)/I2247</f>
+        <v>1.1716627795100207</v>
+      </c>
+      <c r="K2247">
+        <f t="shared" si="95"/>
+        <v>1.8607166400000004</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2248" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B2248">
+        <v>1749.79</v>
+      </c>
+      <c r="C2248">
+        <v>1770</v>
+      </c>
+      <c r="D2248">
+        <v>1737.53</v>
+      </c>
+      <c r="E2248">
+        <v>1749.91</v>
+      </c>
+      <c r="F2248">
+        <f t="shared" si="94"/>
+        <v>1.7499100000000001</v>
+      </c>
+      <c r="G2248">
+        <v>300353458</v>
+      </c>
+      <c r="H2248" s="3">
+        <v>560137000000</v>
+      </c>
+      <c r="I2248">
+        <f t="shared" si="91"/>
+        <v>2246</v>
+      </c>
+      <c r="J2248">
+        <f>SUM($F$3:F2248)/I2248</f>
+        <v>1.1719202359750651</v>
+      </c>
+      <c r="K2248">
+        <f t="shared" si="95"/>
+        <v>1.8615198400000001</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2249" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B2249">
+        <v>1758.7</v>
+      </c>
+      <c r="C2249">
+        <v>1787.91</v>
+      </c>
+      <c r="D2249">
+        <v>1758.7</v>
+      </c>
+      <c r="E2249">
+        <v>1785.13</v>
+      </c>
+      <c r="F2249">
+        <f t="shared" si="94"/>
+        <v>1.7851300000000001</v>
+      </c>
+      <c r="G2249">
+        <v>277552056</v>
+      </c>
+      <c r="H2249" s="3">
+        <v>528932000000</v>
+      </c>
+      <c r="I2249">
+        <f t="shared" si="91"/>
+        <v>2247</v>
+      </c>
+      <c r="J2249">
+        <f>SUM($F$3:F2249)/I2249</f>
+        <v>1.1721931375166874</v>
+      </c>
+      <c r="K2249">
+        <f t="shared" si="95"/>
+        <v>1.8624134800000003</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2250" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B2250">
+        <v>1783.22</v>
+      </c>
+      <c r="C2250">
+        <v>1800.53</v>
+      </c>
+      <c r="D2250">
+        <v>1764.11</v>
+      </c>
+      <c r="E2250">
+        <v>1797.37</v>
+      </c>
+      <c r="F2250">
+        <f t="shared" si="94"/>
+        <v>1.7973699999999999</v>
+      </c>
+      <c r="G2250">
+        <v>271038554</v>
+      </c>
+      <c r="H2250" s="3">
+        <v>516991000000</v>
+      </c>
+      <c r="I2250">
+        <f t="shared" si="91"/>
+        <v>2248</v>
+      </c>
+      <c r="J2250">
+        <f>SUM($F$3:F2250)/I2250</f>
+        <v>1.1724712411032012</v>
+      </c>
+      <c r="K2250">
+        <f t="shared" si="95"/>
+        <v>1.8632790000000001</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2251" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B2251">
+        <v>1789.04</v>
+      </c>
+      <c r="C2251">
+        <v>1794.35</v>
+      </c>
+      <c r="D2251">
+        <v>1775.04</v>
+      </c>
+      <c r="E2251">
+        <v>1787.6</v>
+      </c>
+      <c r="F2251">
+        <f t="shared" si="94"/>
+        <v>1.7875999999999999</v>
+      </c>
+      <c r="G2251">
+        <v>261265519</v>
+      </c>
+      <c r="H2251" s="3">
+        <v>526844000000</v>
+      </c>
+      <c r="I2251">
+        <f t="shared" si="91"/>
+        <v>2249</v>
+      </c>
+      <c r="J2251">
+        <f>SUM($F$3:F2251)/I2251</f>
+        <v>1.1727447532236535</v>
+      </c>
+      <c r="K2251">
+        <f t="shared" si="95"/>
+        <v>1.8641166000000005</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2252" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B2252">
+        <v>1782.34</v>
+      </c>
+      <c r="C2252">
+        <v>1804.89</v>
+      </c>
+      <c r="D2252">
+        <v>1768.49</v>
+      </c>
+      <c r="E2252">
+        <v>1791.19</v>
+      </c>
+      <c r="F2252">
+        <f t="shared" si="94"/>
+        <v>1.7911900000000001</v>
+      </c>
+      <c r="G2252">
+        <v>296131753</v>
+      </c>
+      <c r="H2252" s="3">
+        <v>640108000000</v>
+      </c>
+      <c r="I2252">
+        <f t="shared" si="91"/>
+        <v>2250</v>
+      </c>
+      <c r="J2252">
+        <f>SUM($F$3:F2252)/I2252</f>
+        <v>1.1730196177777761</v>
+      </c>
+      <c r="K2252">
+        <f t="shared" si="95"/>
+        <v>1.8648833200000003</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2253" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B2253">
+        <v>1787.21</v>
+      </c>
+      <c r="C2253">
+        <v>1804.67</v>
+      </c>
+      <c r="D2253">
+        <v>1742.18</v>
+      </c>
+      <c r="E2253">
+        <v>1804.44</v>
+      </c>
+      <c r="F2253">
+        <f t="shared" si="94"/>
+        <v>1.80444</v>
+      </c>
+      <c r="G2253">
+        <v>347248455</v>
+      </c>
+      <c r="H2253" s="3">
+        <v>708620000000</v>
+      </c>
+      <c r="I2253">
+        <f t="shared" si="91"/>
+        <v>2251</v>
+      </c>
+      <c r="J2253">
+        <f>SUM($F$3:F2253)/I2253</f>
+        <v>1.1733001243891588</v>
+      </c>
+      <c r="K2253">
+        <f t="shared" si="95"/>
+        <v>1.8657810400000003</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2254" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B2254">
+        <v>1793.96</v>
+      </c>
+      <c r="C2254">
+        <v>1823.58</v>
+      </c>
+      <c r="D2254">
+        <v>1785.55</v>
+      </c>
+      <c r="E2254">
+        <v>1795.38</v>
+      </c>
+      <c r="F2254">
+        <f t="shared" si="94"/>
+        <v>1.7953800000000002</v>
+      </c>
+      <c r="G2254">
+        <v>305842972</v>
+      </c>
+      <c r="H2254" s="3">
+        <v>624578000000</v>
+      </c>
+      <c r="I2254">
+        <f t="shared" si="91"/>
+        <v>2252</v>
+      </c>
+      <c r="J2254">
+        <f>SUM($F$3:F2254)/I2254</f>
+        <v>1.173576358792183</v>
+      </c>
+      <c r="K2254">
+        <f t="shared" si="95"/>
+        <v>1.8666020800000001</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2255" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B2255">
+        <v>1789.11</v>
+      </c>
+      <c r="C2255">
+        <v>1790.28</v>
+      </c>
+      <c r="D2255">
+        <v>1748.78</v>
+      </c>
+      <c r="E2255">
+        <v>1774.29</v>
+      </c>
+      <c r="F2255">
+        <f t="shared" si="94"/>
+        <v>1.7742899999999999</v>
+      </c>
+      <c r="G2255">
+        <v>289658274</v>
+      </c>
+      <c r="H2255" s="3">
+        <v>602552000000</v>
+      </c>
+      <c r="I2255">
+        <f t="shared" si="91"/>
+        <v>2253</v>
+      </c>
+      <c r="J2255">
+        <f>SUM($F$3:F2255)/I2255</f>
+        <v>1.1738429871282716</v>
+      </c>
+      <c r="K2255">
+        <f t="shared" si="95"/>
+        <v>1.8673126000000004</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2256" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B2256">
+        <v>1770.24</v>
+      </c>
+      <c r="C2256">
+        <v>1772.18</v>
+      </c>
+      <c r="D2256">
+        <v>1736.54</v>
+      </c>
+      <c r="E2256">
+        <v>1745.05</v>
+      </c>
+      <c r="F2256">
+        <f t="shared" si="94"/>
+        <v>1.74505</v>
+      </c>
+      <c r="G2256">
+        <v>306784363</v>
+      </c>
+      <c r="H2256" s="3">
+        <v>669272000000</v>
+      </c>
+      <c r="I2256">
+        <f t="shared" si="91"/>
+        <v>2254</v>
+      </c>
+      <c r="J2256">
+        <f>SUM($F$3:F2256)/I2256</f>
+        <v>1.1740964063886408</v>
+      </c>
+      <c r="K2256">
+        <f t="shared" si="95"/>
+        <v>1.8680505200000004</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2257" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B2257">
+        <v>1735.68</v>
+      </c>
+      <c r="C2257">
+        <v>1735.69</v>
+      </c>
+      <c r="D2257">
+        <v>1692.78</v>
+      </c>
+      <c r="E2257">
+        <v>1692.78</v>
+      </c>
+      <c r="F2257">
+        <f t="shared" si="94"/>
+        <v>1.69278</v>
+      </c>
+      <c r="G2257">
+        <v>315311537</v>
+      </c>
+      <c r="H2257" s="3">
+        <v>670627000000</v>
+      </c>
+      <c r="I2257">
+        <f t="shared" si="91"/>
+        <v>2255</v>
+      </c>
+      <c r="J2257">
+        <f>SUM($F$3:F2257)/I2257</f>
+        <v>1.1743264212860292</v>
+      </c>
+      <c r="K2257">
+        <f t="shared" si="95"/>
+        <v>1.8684730000000005</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2258" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B2258">
+        <v>1690.92</v>
+      </c>
+      <c r="C2258">
+        <v>1696.64</v>
+      </c>
+      <c r="D2258">
+        <v>1662.79</v>
+      </c>
+      <c r="E2258">
+        <v>1690.1</v>
+      </c>
+      <c r="F2258">
+        <f t="shared" si="94"/>
+        <v>1.6900999999999999</v>
+      </c>
+      <c r="G2258">
+        <v>302657282</v>
+      </c>
+      <c r="H2258" s="3">
+        <v>645045000000</v>
+      </c>
+      <c r="I2258">
+        <f t="shared" si="91"/>
+        <v>2256</v>
+      </c>
+      <c r="J2258">
+        <f>SUM($F$3:F2258)/I2258</f>
+        <v>1.1745550443262391</v>
+      </c>
+      <c r="K2258">
+        <f t="shared" si="95"/>
+        <v>1.86889744</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2259" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B2259">
+        <v>1689.2</v>
+      </c>
+      <c r="C2259">
+        <v>1723.48</v>
+      </c>
+      <c r="D2259">
+        <v>1679.37</v>
+      </c>
+      <c r="E2259">
+        <v>1723.13</v>
+      </c>
+      <c r="F2259">
+        <f t="shared" si="94"/>
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="G2259">
+        <v>291783472</v>
+      </c>
+      <c r="H2259" s="3">
+        <v>630798000000</v>
+      </c>
+      <c r="I2259">
+        <f t="shared" si="91"/>
+        <v>2257</v>
+      </c>
+      <c r="J2259">
+        <f>SUM($F$3:F2259)/I2259</f>
+        <v>1.1747980992467859</v>
+      </c>
+      <c r="K2259">
+        <f t="shared" si="95"/>
+        <v>1.8694703600000002</v>
       </c>
     </row>
   </sheetData>
